--- a/02_config/example_single_market/agents.xlsx
+++ b/02_config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="339">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -51,139 +51,139 @@
     <t>general/market_participant</t>
   </si>
   <si>
-    <t>inflexible_load/owner</t>
-  </si>
-  <si>
-    <t>inflexible_load/num</t>
-  </si>
-  <si>
-    <t>inflexible_load/sizing/demand_0</t>
-  </si>
-  <si>
-    <t>inflexible_load/sizing/file_0</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/method</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/naive/offset</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/average/offset</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/average/days</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/smoothed/steps</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/sarma/order</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/cnn/features</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/cnn/days</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/cnn/epoch</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/cnn/window_length</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/rnn/features</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/rnn/days</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/rnn/epoch</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/rnn/window_length</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/rfr/features</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/rfr/days</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/arima/order</t>
-  </si>
-  <si>
-    <t>inflexible_load/fcast/arima/days</t>
-  </si>
-  <si>
-    <t>flexible_load/owner</t>
-  </si>
-  <si>
-    <t>flexible_load/num</t>
-  </si>
-  <si>
-    <t>flexible_load/sizing/demand_0</t>
-  </si>
-  <si>
-    <t>flexible_load/sizing/file_0</t>
-  </si>
-  <si>
-    <t>flexible_load/sizing/time_offset_0</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/method</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/naive/offset</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/average/offset</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/average/days</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/smoothed/steps</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/sarma/order</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/cnn/features</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/cnn/days</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/cnn/epoch</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/cnn/window_length</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/rnn/features</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/rnn/days</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/rnn/epoch</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/rnn/window_length</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/rfr/features</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/rfr/days</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/arima/order</t>
-  </si>
-  <si>
-    <t>flexible_load/fcast/arima/days</t>
+    <t>inflexible-load/owner</t>
+  </si>
+  <si>
+    <t>inflexible-load/num</t>
+  </si>
+  <si>
+    <t>inflexible-load/sizing/demand_0</t>
+  </si>
+  <si>
+    <t>inflexible-load/sizing/file_0</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/method</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/naive/offset</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/average/offset</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/average/days</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/smoothed/steps</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/sarma/order</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/cnn/features</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/cnn/days</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/cnn/epoch</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/cnn/window_length</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/rnn/features</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/rnn/days</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/rnn/epoch</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/rnn/window_length</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/rfr/features</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/rfr/days</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/arima/order</t>
+  </si>
+  <si>
+    <t>inflexible-load/fcast/arima/days</t>
+  </si>
+  <si>
+    <t>flexible-load/owner</t>
+  </si>
+  <si>
+    <t>flexible-load/num</t>
+  </si>
+  <si>
+    <t>flexible-load/sizing/demand_0</t>
+  </si>
+  <si>
+    <t>flexible-load/sizing/file_0</t>
+  </si>
+  <si>
+    <t>flexible-load/sizing/time_offset_0</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/method</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/naive/offset</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/average/offset</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/average/days</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/smoothed/steps</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/sarma/order</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/cnn/features</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/cnn/days</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/cnn/epoch</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/cnn/window_length</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/rnn/features</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/rnn/days</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/rnn/epoch</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/rnn/window_length</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/rfr/features</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/rfr/days</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/arima/order</t>
+  </si>
+  <si>
+    <t>flexible-load/fcast/arima/days</t>
   </si>
   <si>
     <t>heat/owner</t>
@@ -471,76 +471,76 @@
     <t>wind/quality</t>
   </si>
   <si>
-    <t>fixed_gen/owner</t>
-  </si>
-  <si>
-    <t>fixed_gen/num</t>
-  </si>
-  <si>
-    <t>fixed_gen/sizing/power_0</t>
-  </si>
-  <si>
-    <t>fixed_gen/sizing/file_0</t>
-  </si>
-  <si>
-    <t>fixed_gen/sizing/controllable_0</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/method</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/naive/offset</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/average/offset</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/average/days</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/smoothed/steps</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/sarma/order</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/cnn/features</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/cnn/days</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/cnn/epoch</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/cnn/window_length</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/rnn/features</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/rnn/days</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/rnn/epoch</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/rnn/window_length</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/rfr/features</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/rfr/days</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/arima/order</t>
-  </si>
-  <si>
-    <t>fixed_gen/fcast/arima/days</t>
-  </si>
-  <si>
-    <t>fixed_gen/quality</t>
+    <t>fixed-gen/owner</t>
+  </si>
+  <si>
+    <t>fixed-gen/num</t>
+  </si>
+  <si>
+    <t>fixed-gen/sizing/power_0</t>
+  </si>
+  <si>
+    <t>fixed-gen/sizing/file_0</t>
+  </si>
+  <si>
+    <t>fixed-gen/sizing/controllable_0</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/method</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/naive/offset</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/average/offset</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/average/days</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/smoothed/steps</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/sarma/order</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/cnn/features</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/cnn/days</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/cnn/epoch</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/cnn/window_length</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/rnn/features</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/rnn/days</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/rnn/epoch</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/rnn/window_length</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/rfr/features</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/rfr/days</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/arima/order</t>
+  </si>
+  <si>
+    <t>fixed-gen/fcast/arima/days</t>
+  </si>
+  <si>
+    <t>fixed-gen/quality</t>
   </si>
   <si>
     <t>hp/owner</t>
@@ -555,6 +555,60 @@
     <t>hp/sizing/file_0</t>
   </si>
   <si>
+    <t>hp/fcast/method</t>
+  </si>
+  <si>
+    <t>hp/fcast/naive/offset</t>
+  </si>
+  <si>
+    <t>hp/fcast/average/offset</t>
+  </si>
+  <si>
+    <t>hp/fcast/average/days</t>
+  </si>
+  <si>
+    <t>hp/fcast/smoothed/steps</t>
+  </si>
+  <si>
+    <t>hp/fcast/sarma/order</t>
+  </si>
+  <si>
+    <t>hp/fcast/cnn/features</t>
+  </si>
+  <si>
+    <t>hp/fcast/cnn/days</t>
+  </si>
+  <si>
+    <t>hp/fcast/cnn/epoch</t>
+  </si>
+  <si>
+    <t>hp/fcast/cnn/window_length</t>
+  </si>
+  <si>
+    <t>hp/fcast/rnn/features</t>
+  </si>
+  <si>
+    <t>hp/fcast/rnn/days</t>
+  </si>
+  <si>
+    <t>hp/fcast/rnn/epoch</t>
+  </si>
+  <si>
+    <t>hp/fcast/rnn/window_length</t>
+  </si>
+  <si>
+    <t>hp/fcast/rfr/features</t>
+  </si>
+  <si>
+    <t>hp/fcast/rfr/days</t>
+  </si>
+  <si>
+    <t>hp/fcast/arima/order</t>
+  </si>
+  <si>
+    <t>hp/fcast/arima/days</t>
+  </si>
+  <si>
     <t>hp/quality</t>
   </si>
   <si>
@@ -669,25 +723,25 @@
     <t>battery/quality</t>
   </si>
   <si>
-    <t>heat_storage/owner</t>
-  </si>
-  <si>
-    <t>heat_storage/num</t>
-  </si>
-  <si>
-    <t>heat_storage/sizing/power_0</t>
-  </si>
-  <si>
-    <t>heat_storage/sizing/capacity_0</t>
-  </si>
-  <si>
-    <t>heat_storage/sizing/efficiency_0</t>
-  </si>
-  <si>
-    <t>heat_storage/sizing/soc_0</t>
-  </si>
-  <si>
-    <t>heat_storage/quality</t>
+    <t>heat-storage/owner</t>
+  </si>
+  <si>
+    <t>heat-storage/num</t>
+  </si>
+  <si>
+    <t>heat-storage/sizing/power_0</t>
+  </si>
+  <si>
+    <t>heat-storage/sizing/capacity_0</t>
+  </si>
+  <si>
+    <t>heat-storage/sizing/efficiency_0</t>
+  </si>
+  <si>
+    <t>heat-storage/sizing/soc_0</t>
+  </si>
+  <si>
+    <t>heat-storage/quality</t>
   </si>
   <si>
     <t>ems/controller/rtc/method</t>
@@ -741,55 +795,55 @@
     <t>ems/fcasts/update</t>
   </si>
   <si>
-    <t>6amLPGSnTedGjou</t>
-  </si>
-  <si>
-    <t>gQ7Sq3ucg78n4e2</t>
-  </si>
-  <si>
-    <t>0O9n4HIGxRrV58t</t>
-  </si>
-  <si>
-    <t>khzFYYWbb9gU6bQ</t>
-  </si>
-  <si>
-    <t>42KvQZD9ht2Hf7I</t>
-  </si>
-  <si>
-    <t>KO0lC3dN9zUuBwS</t>
-  </si>
-  <si>
-    <t>W16FZ8BxcyuuvrL</t>
-  </si>
-  <si>
-    <t>9l37kMNMXWcA0Nm</t>
-  </si>
-  <si>
-    <t>JHwCQsEwLJG3EbF</t>
-  </si>
-  <si>
-    <t>wi68hZKelP3cqgt</t>
+    <t>o8RENvmIJHHNd1l</t>
+  </si>
+  <si>
+    <t>I90EqWRtDwkBV26</t>
+  </si>
+  <si>
+    <t>A0hRymeCrOZSb8w</t>
+  </si>
+  <si>
+    <t>FOSMD7SSeMwEjUC</t>
+  </si>
+  <si>
+    <t>67aIDazktWn6yzC</t>
+  </si>
+  <si>
+    <t>vMMDGls8ojIM2vT</t>
+  </si>
+  <si>
+    <t>ypY3kBiRXLP0Gfn</t>
+  </si>
+  <si>
+    <t>HqZsrPIjCXt8ECE</t>
+  </si>
+  <si>
+    <t>dEY0eRjw9O27gIv</t>
+  </si>
+  <si>
+    <t>SekGK0Bo2wtyeck</t>
+  </si>
+  <si>
+    <t>hh_4536_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2896_0.csv</t>
   </si>
   <si>
     <t>hh_5527_0.csv</t>
   </si>
   <si>
+    <t>hh_3648_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
     <t>hh_4402_0.csv</t>
   </si>
   <si>
-    <t>hh_2959_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2687_0.csv</t>
+    <t>hh_2532_0.csv</t>
   </si>
   <si>
     <t>perfect</t>
@@ -807,6 +861,33 @@
     <t>rfr</t>
   </si>
   <si>
+    <t>heat_4536_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2896_0.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3125_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_4402_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
     <t>naive</t>
   </si>
   <si>
@@ -825,19 +906,28 @@
     <t>local</t>
   </si>
   <si>
-    <t>ev_fulltime_43.csv</t>
+    <t>hp_Bosch Thermotechnik_air.json</t>
+  </si>
+  <si>
+    <t>hp_DAIKIN Europe_ground.json</t>
+  </si>
+  <si>
+    <t>ev_freetime_1.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_46.csv</t>
   </si>
   <si>
     <t>ev_freetime_3.csv</t>
   </si>
   <si>
-    <t>ev_parttime_88.csv</t>
-  </si>
-  <si>
     <t>ev_parttime_89.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_48.csv</t>
   </si>
   <si>
     <t>min_soc</t>
@@ -1303,10 +1393,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:IG11"/>
+  <dimension ref="A1:IY11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:241">
+    <row r="1" spans="1:259">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2027,13 +2117,67 @@
       <c r="IG1" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="IH1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="II1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="IJ1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="IK1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="IL1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="IM1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="IN1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="IO1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="IP1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="IQ1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="IR1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="IS1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="IT1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="IU1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="IV1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="IW1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="IX1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="IY1" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
-    <row r="2" spans="1:241">
+    <row r="2" spans="1:259">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -2060,13 +2204,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>5527000</v>
+        <v>4536000</v>
       </c>
       <c r="O2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="P2" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2081,10 +2225,10 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W2">
         <v>3</v>
@@ -2096,7 +2240,7 @@
         <v>20</v>
       </c>
       <c r="Z2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA2">
         <v>3</v>
@@ -2108,13 +2252,13 @@
         <v>20</v>
       </c>
       <c r="AD2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE2">
         <v>3</v>
       </c>
       <c r="AF2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG2">
         <v>3</v>
@@ -2129,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="AM2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -2144,10 +2288,10 @@
         <v>9</v>
       </c>
       <c r="AR2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT2">
         <v>3</v>
@@ -2159,7 +2303,7 @@
         <v>20</v>
       </c>
       <c r="AW2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX2">
         <v>3</v>
@@ -2171,25 +2315,34 @@
         <v>20</v>
       </c>
       <c r="BA2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB2">
         <v>3</v>
       </c>
       <c r="BC2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD2">
         <v>3</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG2">
+        <v>19500000</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BI2">
+        <v>35</v>
       </c>
       <c r="BJ2" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK2">
         <v>1</v>
@@ -2204,10 +2357,10 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ2">
         <v>3</v>
@@ -2219,7 +2372,7 @@
         <v>20</v>
       </c>
       <c r="BT2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU2">
         <v>3</v>
@@ -2231,13 +2384,13 @@
         <v>20</v>
       </c>
       <c r="BX2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY2">
         <v>3</v>
       </c>
       <c r="BZ2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -2246,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="CF2" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG2">
         <v>1</v>
@@ -2261,10 +2414,10 @@
         <v>9</v>
       </c>
       <c r="CK2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM2">
         <v>3</v>
@@ -2276,7 +2429,7 @@
         <v>20</v>
       </c>
       <c r="CP2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ2">
         <v>3</v>
@@ -2288,13 +2441,13 @@
         <v>20</v>
       </c>
       <c r="CT2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU2">
         <v>3</v>
       </c>
       <c r="CV2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW2">
         <v>3</v>
@@ -2306,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="DE2" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF2">
         <v>1</v>
@@ -2321,10 +2474,10 @@
         <v>9</v>
       </c>
       <c r="DJ2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL2">
         <v>3</v>
@@ -2336,7 +2489,7 @@
         <v>20</v>
       </c>
       <c r="DO2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP2">
         <v>3</v>
@@ -2348,19 +2501,19 @@
         <v>20</v>
       </c>
       <c r="DS2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT2">
         <v>3</v>
       </c>
       <c r="DU2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV2">
         <v>3</v>
       </c>
       <c r="DW2" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX2">
         <v>0</v>
@@ -2369,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -2384,10 +2537,10 @@
         <v>9</v>
       </c>
       <c r="EH2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ2">
         <v>3</v>
@@ -2399,7 +2552,7 @@
         <v>20</v>
       </c>
       <c r="EM2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN2">
         <v>3</v>
@@ -2411,19 +2564,19 @@
         <v>20</v>
       </c>
       <c r="EQ2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER2">
         <v>3</v>
       </c>
       <c r="ES2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET2">
         <v>3</v>
       </c>
       <c r="EU2" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV2">
         <v>0</v>
@@ -2432,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="FA2" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB2">
         <v>1</v>
@@ -2447,222 +2600,294 @@
         <v>9</v>
       </c>
       <c r="FF2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG2" t="s">
+        <v>277</v>
+      </c>
+      <c r="FH2">
+        <v>3</v>
+      </c>
+      <c r="FI2">
+        <v>20</v>
+      </c>
+      <c r="FJ2">
+        <v>20</v>
+      </c>
+      <c r="FK2" t="s">
+        <v>277</v>
+      </c>
+      <c r="FL2">
+        <v>3</v>
+      </c>
+      <c r="FM2">
+        <v>20</v>
+      </c>
+      <c r="FN2">
+        <v>20</v>
+      </c>
+      <c r="FO2" t="s">
+        <v>277</v>
+      </c>
+      <c r="FP2">
+        <v>3</v>
+      </c>
+      <c r="FQ2" t="s">
+        <v>278</v>
+      </c>
+      <c r="FR2">
+        <v>3</v>
+      </c>
+      <c r="FS2" t="s">
+        <v>294</v>
+      </c>
+      <c r="FT2">
+        <v>1</v>
+      </c>
+      <c r="FU2">
+        <v>1</v>
+      </c>
+      <c r="FV2">
+        <v>9800</v>
+      </c>
+      <c r="FW2" t="s">
+        <v>295</v>
+      </c>
+      <c r="FX2" t="s">
+        <v>275</v>
+      </c>
+      <c r="FY2">
+        <v>1</v>
+      </c>
+      <c r="FZ2">
+        <v>1</v>
+      </c>
+      <c r="GA2">
+        <v>2</v>
+      </c>
+      <c r="GB2">
+        <v>9</v>
+      </c>
+      <c r="GC2" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD2" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE2">
+        <v>3</v>
+      </c>
+      <c r="GF2">
+        <v>20</v>
+      </c>
+      <c r="GG2">
+        <v>20</v>
+      </c>
+      <c r="GH2" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI2">
+        <v>3</v>
+      </c>
+      <c r="GJ2">
+        <v>20</v>
+      </c>
+      <c r="GK2">
+        <v>20</v>
+      </c>
+      <c r="GL2" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM2">
+        <v>3</v>
+      </c>
+      <c r="GN2" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO2">
+        <v>3</v>
+      </c>
+      <c r="GP2" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ2">
+        <v>1</v>
+      </c>
+      <c r="GR2">
+        <v>2</v>
+      </c>
+      <c r="GS2" t="s">
+        <v>297</v>
+      </c>
+      <c r="GT2">
+        <v>75000</v>
+      </c>
+      <c r="GU2">
+        <v>7200</v>
+      </c>
+      <c r="GV2">
+        <v>11000</v>
+      </c>
+      <c r="GW2">
+        <v>100000</v>
+      </c>
+      <c r="GX2">
+        <v>0.9</v>
+      </c>
+      <c r="GY2">
+        <v>0.8</v>
+      </c>
+      <c r="GZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="HA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="HB2" t="s">
+        <v>302</v>
+      </c>
+      <c r="HC2">
+        <v>100000</v>
+      </c>
+      <c r="HD2">
+        <v>11000</v>
+      </c>
+      <c r="HE2">
+        <v>22000</v>
+      </c>
+      <c r="HF2">
+        <v>200000</v>
+      </c>
+      <c r="HG2">
+        <v>0.9</v>
+      </c>
+      <c r="HH2">
+        <v>0.8</v>
+      </c>
+      <c r="HI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="HJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="HK2" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL2">
+        <v>0.05</v>
+      </c>
+      <c r="HM2">
+        <v>0.5</v>
+      </c>
+      <c r="HN2">
+        <v>0.8</v>
+      </c>
+      <c r="HO2">
+        <v>8.5</v>
+      </c>
+      <c r="HP2" t="s">
+        <v>304</v>
+      </c>
+      <c r="HQ2" t="s">
+        <v>305</v>
+      </c>
+      <c r="HR2" t="s">
+        <v>294</v>
+      </c>
+      <c r="HS2">
+        <v>0</v>
+      </c>
+      <c r="HT2">
+        <v>0</v>
+      </c>
+      <c r="IA2" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB2">
+        <v>1</v>
+      </c>
+      <c r="IC2">
+        <v>1</v>
+      </c>
+      <c r="ID2">
+        <v>9800</v>
+      </c>
+      <c r="IE2">
+        <v>19500</v>
+      </c>
+      <c r="IF2">
+        <v>0.95</v>
+      </c>
+      <c r="IG2">
+        <v>0.5</v>
+      </c>
+      <c r="IH2" t="s">
+        <v>294</v>
+      </c>
+      <c r="II2" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ2" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK2">
+        <v>86400</v>
+      </c>
+      <c r="IL2" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM2">
+        <v>86400</v>
+      </c>
+      <c r="IN2" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO2">
+        <v>1</v>
+      </c>
+      <c r="IP2" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ2">
+        <v>1</v>
+      </c>
+      <c r="IR2" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS2" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT2" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU2" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV2" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW2">
+        <v>86400</v>
+      </c>
+      <c r="IX2">
+        <v>86400</v>
+      </c>
+      <c r="IY2">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:259">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>259</v>
       </c>
-      <c r="FH2">
-        <v>3</v>
-      </c>
-      <c r="FI2">
-        <v>20</v>
-      </c>
-      <c r="FJ2">
-        <v>20</v>
-      </c>
-      <c r="FK2" t="s">
-        <v>259</v>
-      </c>
-      <c r="FL2">
-        <v>3</v>
-      </c>
-      <c r="FM2">
-        <v>20</v>
-      </c>
-      <c r="FN2">
-        <v>20</v>
-      </c>
-      <c r="FO2" t="s">
-        <v>259</v>
-      </c>
-      <c r="FP2">
-        <v>3</v>
-      </c>
-      <c r="FQ2" t="s">
-        <v>260</v>
-      </c>
-      <c r="FR2">
-        <v>3</v>
-      </c>
-      <c r="FS2" t="s">
-        <v>267</v>
-      </c>
-      <c r="FT2">
-        <v>0</v>
-      </c>
-      <c r="FU2">
-        <v>0</v>
-      </c>
-      <c r="FX2" t="s">
-        <v>267</v>
-      </c>
-      <c r="FY2">
-        <v>1</v>
-      </c>
-      <c r="FZ2">
-        <v>2</v>
-      </c>
-      <c r="GA2" t="s">
-        <v>268</v>
-      </c>
-      <c r="GB2">
-        <v>50000</v>
-      </c>
-      <c r="GC2">
-        <v>7200</v>
-      </c>
-      <c r="GD2">
-        <v>7200</v>
-      </c>
-      <c r="GE2">
-        <v>50000</v>
-      </c>
-      <c r="GF2">
-        <v>0.9</v>
-      </c>
-      <c r="GG2">
-        <v>0.8</v>
-      </c>
-      <c r="GH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GJ2" t="s">
-        <v>272</v>
-      </c>
-      <c r="GK2">
-        <v>100000</v>
-      </c>
-      <c r="GL2">
-        <v>11000</v>
-      </c>
-      <c r="GM2">
-        <v>22000</v>
-      </c>
-      <c r="GN2">
-        <v>200000</v>
-      </c>
-      <c r="GO2">
-        <v>0.9</v>
-      </c>
-      <c r="GP2">
-        <v>0.8</v>
-      </c>
-      <c r="GQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GS2" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT2">
-        <v>0.05</v>
-      </c>
-      <c r="GU2">
-        <v>0.5</v>
-      </c>
-      <c r="GV2">
-        <v>0.8</v>
-      </c>
-      <c r="GW2">
-        <v>8.5</v>
-      </c>
-      <c r="GX2" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY2" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ2" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA2">
-        <v>0</v>
-      </c>
-      <c r="HB2">
-        <v>0</v>
-      </c>
-      <c r="HI2" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ2">
-        <v>0</v>
-      </c>
-      <c r="HK2">
-        <v>0</v>
-      </c>
-      <c r="HP2" t="s">
-        <v>267</v>
-      </c>
-      <c r="HQ2" t="s">
-        <v>276</v>
-      </c>
-      <c r="HR2" t="s">
-        <v>276</v>
-      </c>
-      <c r="HS2">
-        <v>86400</v>
-      </c>
-      <c r="HT2" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU2">
-        <v>86400</v>
-      </c>
-      <c r="HV2" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW2">
-        <v>1</v>
-      </c>
-      <c r="HX2" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY2">
-        <v>1</v>
-      </c>
-      <c r="HZ2" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA2" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB2" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC2" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID2" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE2">
-        <v>86400</v>
-      </c>
-      <c r="IF2">
-        <v>86400</v>
-      </c>
-      <c r="IG2">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:241">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>241</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2671,7 +2896,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2683,13 +2908,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>4402000</v>
+        <v>2896000</v>
       </c>
       <c r="O3" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="P3" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2704,10 +2929,10 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -2719,7 +2944,7 @@
         <v>20</v>
       </c>
       <c r="Z3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA3">
         <v>3</v>
@@ -2731,13 +2956,13 @@
         <v>20</v>
       </c>
       <c r="AD3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE3">
         <v>3</v>
       </c>
       <c r="AF3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG3">
         <v>3</v>
@@ -2752,7 +2977,7 @@
         <v>6</v>
       </c>
       <c r="AM3" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -2767,10 +2992,10 @@
         <v>9</v>
       </c>
       <c r="AR3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT3">
         <v>3</v>
@@ -2782,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="AW3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX3">
         <v>3</v>
@@ -2794,25 +3019,34 @@
         <v>20</v>
       </c>
       <c r="BA3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB3">
         <v>3</v>
       </c>
       <c r="BC3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD3">
         <v>3</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG3">
+        <v>19500000</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>281</v>
+      </c>
+      <c r="BI3">
+        <v>55</v>
       </c>
       <c r="BJ3" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK3">
         <v>1</v>
@@ -2827,10 +3061,10 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ3">
         <v>3</v>
@@ -2842,7 +3076,7 @@
         <v>20</v>
       </c>
       <c r="BT3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU3">
         <v>3</v>
@@ -2854,13 +3088,13 @@
         <v>20</v>
       </c>
       <c r="BX3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY3">
         <v>3</v>
       </c>
       <c r="BZ3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA3">
         <v>0</v>
@@ -2869,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="CF3" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG3">
         <v>1</v>
@@ -2884,10 +3118,10 @@
         <v>9</v>
       </c>
       <c r="CK3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM3">
         <v>3</v>
@@ -2899,7 +3133,7 @@
         <v>20</v>
       </c>
       <c r="CP3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ3">
         <v>3</v>
@@ -2911,13 +3145,13 @@
         <v>20</v>
       </c>
       <c r="CT3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU3">
         <v>3</v>
       </c>
       <c r="CV3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW3">
         <v>3</v>
@@ -2929,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="DE3" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF3">
         <v>1</v>
@@ -2944,10 +3178,10 @@
         <v>9</v>
       </c>
       <c r="DJ3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL3">
         <v>3</v>
@@ -2959,7 +3193,7 @@
         <v>20</v>
       </c>
       <c r="DO3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP3">
         <v>3</v>
@@ -2971,19 +3205,19 @@
         <v>20</v>
       </c>
       <c r="DS3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT3">
         <v>3</v>
       </c>
       <c r="DU3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV3">
         <v>3</v>
       </c>
       <c r="DW3" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX3">
         <v>0</v>
@@ -2992,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED3">
         <v>1</v>
@@ -3007,10 +3241,10 @@
         <v>9</v>
       </c>
       <c r="EH3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ3">
         <v>3</v>
@@ -3022,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="EM3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN3">
         <v>3</v>
@@ -3034,19 +3268,19 @@
         <v>20</v>
       </c>
       <c r="EQ3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER3">
         <v>3</v>
       </c>
       <c r="ES3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET3">
         <v>3</v>
       </c>
       <c r="EU3" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV3">
         <v>0</v>
@@ -3055,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="FA3" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB3">
         <v>1</v>
@@ -3070,10 +3304,10 @@
         <v>9</v>
       </c>
       <c r="FF3" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH3">
         <v>3</v>
@@ -3085,7 +3319,7 @@
         <v>20</v>
       </c>
       <c r="FK3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL3">
         <v>3</v>
@@ -3097,28 +3331,34 @@
         <v>20</v>
       </c>
       <c r="FO3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP3">
         <v>3</v>
       </c>
       <c r="FQ3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR3">
         <v>3</v>
       </c>
       <c r="FS3" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV3">
+        <v>9800</v>
+      </c>
+      <c r="FW3" t="s">
+        <v>295</v>
       </c>
       <c r="FX3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY3">
         <v>1</v>
@@ -3126,133 +3366,199 @@
       <c r="FZ3">
         <v>1</v>
       </c>
-      <c r="GA3" t="s">
-        <v>269</v>
+      <c r="GA3">
+        <v>2</v>
       </c>
       <c r="GB3">
+        <v>9</v>
+      </c>
+      <c r="GC3" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD3" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE3">
+        <v>3</v>
+      </c>
+      <c r="GF3">
+        <v>20</v>
+      </c>
+      <c r="GG3">
+        <v>20</v>
+      </c>
+      <c r="GH3" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI3">
+        <v>3</v>
+      </c>
+      <c r="GJ3">
+        <v>20</v>
+      </c>
+      <c r="GK3">
+        <v>20</v>
+      </c>
+      <c r="GL3" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM3">
+        <v>3</v>
+      </c>
+      <c r="GN3" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO3">
+        <v>3</v>
+      </c>
+      <c r="GP3" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ3">
+        <v>1</v>
+      </c>
+      <c r="GR3">
+        <v>1</v>
+      </c>
+      <c r="GS3" t="s">
+        <v>298</v>
+      </c>
+      <c r="GT3">
         <v>75000</v>
       </c>
-      <c r="GC3">
+      <c r="GU3">
         <v>7200</v>
       </c>
-      <c r="GD3">
+      <c r="GV3">
         <v>11000</v>
       </c>
-      <c r="GE3">
+      <c r="GW3">
         <v>100000</v>
       </c>
-      <c r="GF3">
+      <c r="GX3">
         <v>0.9</v>
       </c>
-      <c r="GG3">
+      <c r="GY3">
         <v>0.8</v>
       </c>
-      <c r="GH3" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="GS3" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT3">
+      <c r="GZ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="HA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="HK3" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL3">
         <v>0.05</v>
       </c>
-      <c r="GU3">
+      <c r="HM3">
         <v>0.5</v>
       </c>
-      <c r="GV3">
+      <c r="HN3">
         <v>0.8</v>
       </c>
-      <c r="GW3">
+      <c r="HO3">
         <v>8.5</v>
       </c>
-      <c r="GX3" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY3" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ3" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA3">
-        <v>0</v>
-      </c>
-      <c r="HB3">
-        <v>0</v>
-      </c>
-      <c r="HI3" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ3">
-        <v>0</v>
-      </c>
-      <c r="HK3">
-        <v>0</v>
-      </c>
       <c r="HP3" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="HQ3" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="HR3" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="HS3">
+        <v>0</v>
+      </c>
+      <c r="HT3">
+        <v>0</v>
+      </c>
+      <c r="IA3" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB3">
+        <v>1</v>
+      </c>
+      <c r="IC3">
+        <v>1</v>
+      </c>
+      <c r="ID3">
+        <v>9800</v>
+      </c>
+      <c r="IE3">
+        <v>19500</v>
+      </c>
+      <c r="IF3">
+        <v>0.95</v>
+      </c>
+      <c r="IG3">
+        <v>0.5</v>
+      </c>
+      <c r="IH3" t="s">
+        <v>294</v>
+      </c>
+      <c r="II3" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ3" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK3">
         <v>86400</v>
       </c>
-      <c r="HT3" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU3">
+      <c r="IL3" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM3">
         <v>86400</v>
       </c>
-      <c r="HV3" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW3">
-        <v>1</v>
-      </c>
-      <c r="HX3" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY3">
-        <v>1</v>
-      </c>
-      <c r="HZ3" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA3" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB3" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC3" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID3" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE3">
+      <c r="IN3" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO3">
+        <v>1</v>
+      </c>
+      <c r="IP3" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ3">
+        <v>1</v>
+      </c>
+      <c r="IR3" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS3" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT3" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU3" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV3" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW3">
         <v>86400</v>
       </c>
-      <c r="IF3">
+      <c r="IX3">
         <v>86400</v>
       </c>
-      <c r="IG3">
+      <c r="IY3">
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:241">
+    <row r="4" spans="1:259">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3282,10 +3588,10 @@
         <v>5527000</v>
       </c>
       <c r="O4" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="P4" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3300,10 +3606,10 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -3315,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="Z4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA4">
         <v>3</v>
@@ -3327,13 +3633,13 @@
         <v>20</v>
       </c>
       <c r="AD4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE4">
         <v>3</v>
       </c>
       <c r="AF4" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG4">
         <v>3</v>
@@ -3348,7 +3654,7 @@
         <v>6</v>
       </c>
       <c r="AM4" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -3363,10 +3669,10 @@
         <v>9</v>
       </c>
       <c r="AR4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT4">
         <v>3</v>
@@ -3378,7 +3684,7 @@
         <v>20</v>
       </c>
       <c r="AW4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX4">
         <v>3</v>
@@ -3390,25 +3696,34 @@
         <v>20</v>
       </c>
       <c r="BA4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB4">
         <v>3</v>
       </c>
       <c r="BC4" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD4">
         <v>3</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG4">
+        <v>5500000</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>282</v>
+      </c>
+      <c r="BI4">
+        <v>55</v>
       </c>
       <c r="BJ4" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK4">
         <v>1</v>
@@ -3423,10 +3738,10 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ4">
         <v>3</v>
@@ -3438,7 +3753,7 @@
         <v>20</v>
       </c>
       <c r="BT4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU4">
         <v>3</v>
@@ -3450,13 +3765,13 @@
         <v>20</v>
       </c>
       <c r="BX4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY4">
         <v>3</v>
       </c>
       <c r="BZ4" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA4">
         <v>0</v>
@@ -3465,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="CF4" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG4">
         <v>1</v>
@@ -3480,10 +3795,10 @@
         <v>9</v>
       </c>
       <c r="CK4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM4">
         <v>3</v>
@@ -3495,7 +3810,7 @@
         <v>20</v>
       </c>
       <c r="CP4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ4">
         <v>3</v>
@@ -3507,13 +3822,13 @@
         <v>20</v>
       </c>
       <c r="CT4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU4">
         <v>3</v>
       </c>
       <c r="CV4" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW4">
         <v>3</v>
@@ -3525,22 +3840,22 @@
         <v>1</v>
       </c>
       <c r="CZ4">
-        <v>6700</v>
+        <v>8600</v>
       </c>
       <c r="DA4" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="DB4">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="DC4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DD4" t="b">
         <v>1</v>
       </c>
       <c r="DE4" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF4">
         <v>1</v>
@@ -3555,10 +3870,10 @@
         <v>9</v>
       </c>
       <c r="DJ4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL4">
         <v>3</v>
@@ -3570,7 +3885,7 @@
         <v>20</v>
       </c>
       <c r="DO4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP4">
         <v>3</v>
@@ -3582,19 +3897,19 @@
         <v>20</v>
       </c>
       <c r="DS4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT4">
         <v>3</v>
       </c>
       <c r="DU4" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV4">
         <v>3</v>
       </c>
       <c r="DW4" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX4">
         <v>0</v>
@@ -3603,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED4">
         <v>1</v>
@@ -3618,10 +3933,10 @@
         <v>9</v>
       </c>
       <c r="EH4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ4">
         <v>3</v>
@@ -3633,7 +3948,7 @@
         <v>20</v>
       </c>
       <c r="EM4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN4">
         <v>3</v>
@@ -3645,19 +3960,19 @@
         <v>20</v>
       </c>
       <c r="EQ4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER4">
         <v>3</v>
       </c>
       <c r="ES4" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET4">
         <v>3</v>
       </c>
       <c r="EU4" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV4">
         <v>0</v>
@@ -3666,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="FA4" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB4">
         <v>1</v>
@@ -3681,10 +3996,10 @@
         <v>9</v>
       </c>
       <c r="FF4" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH4">
         <v>3</v>
@@ -3696,7 +4011,7 @@
         <v>20</v>
       </c>
       <c r="FK4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL4">
         <v>3</v>
@@ -3708,28 +4023,34 @@
         <v>20</v>
       </c>
       <c r="FO4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP4">
         <v>3</v>
       </c>
       <c r="FQ4" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR4">
         <v>3</v>
       </c>
       <c r="FS4" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV4">
+        <v>2800</v>
+      </c>
+      <c r="FW4" t="s">
+        <v>295</v>
       </c>
       <c r="FX4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY4">
         <v>1</v>
@@ -3737,157 +4058,178 @@
       <c r="FZ4">
         <v>1</v>
       </c>
-      <c r="GA4" t="s">
-        <v>270</v>
+      <c r="GA4">
+        <v>2</v>
       </c>
       <c r="GB4">
-        <v>100000</v>
-      </c>
-      <c r="GC4">
-        <v>11000</v>
-      </c>
-      <c r="GD4">
-        <v>22000</v>
+        <v>9</v>
+      </c>
+      <c r="GC4" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD4" t="s">
+        <v>277</v>
       </c>
       <c r="GE4">
-        <v>200000</v>
+        <v>3</v>
       </c>
       <c r="GF4">
-        <v>0.9</v>
+        <v>20</v>
       </c>
       <c r="GG4">
+        <v>20</v>
+      </c>
+      <c r="GH4" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI4">
+        <v>3</v>
+      </c>
+      <c r="GJ4">
+        <v>20</v>
+      </c>
+      <c r="GK4">
+        <v>20</v>
+      </c>
+      <c r="GL4" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM4">
+        <v>3</v>
+      </c>
+      <c r="GN4" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO4">
+        <v>3</v>
+      </c>
+      <c r="GP4" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ4">
+        <v>0</v>
+      </c>
+      <c r="GR4">
+        <v>0</v>
+      </c>
+      <c r="HK4" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL4">
+        <v>0.05</v>
+      </c>
+      <c r="HM4">
+        <v>0.5</v>
+      </c>
+      <c r="HN4">
         <v>0.8</v>
       </c>
-      <c r="GH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="GS4" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT4">
-        <v>0.05</v>
-      </c>
-      <c r="GU4">
+      <c r="HO4">
+        <v>8.5</v>
+      </c>
+      <c r="HP4" t="s">
+        <v>304</v>
+      </c>
+      <c r="HQ4" t="s">
+        <v>305</v>
+      </c>
+      <c r="HR4" t="s">
+        <v>294</v>
+      </c>
+      <c r="HS4">
+        <v>0</v>
+      </c>
+      <c r="HT4">
+        <v>0</v>
+      </c>
+      <c r="IA4" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB4">
+        <v>1</v>
+      </c>
+      <c r="IC4">
+        <v>1</v>
+      </c>
+      <c r="ID4">
+        <v>2800</v>
+      </c>
+      <c r="IE4">
+        <v>5500</v>
+      </c>
+      <c r="IF4">
+        <v>0.95</v>
+      </c>
+      <c r="IG4">
         <v>0.5</v>
       </c>
-      <c r="GV4">
-        <v>0.8</v>
-      </c>
-      <c r="GW4">
-        <v>8.5</v>
-      </c>
-      <c r="GX4" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY4" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ4" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA4">
-        <v>1</v>
-      </c>
-      <c r="HB4">
-        <v>1</v>
-      </c>
-      <c r="HC4">
-        <v>5500</v>
-      </c>
-      <c r="HD4">
-        <v>5500</v>
-      </c>
-      <c r="HE4">
-        <v>0.95</v>
-      </c>
-      <c r="HF4">
-        <v>0.1</v>
-      </c>
-      <c r="HG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="HI4" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ4">
-        <v>0</v>
-      </c>
-      <c r="HK4">
-        <v>0</v>
-      </c>
-      <c r="HP4" t="s">
-        <v>267</v>
-      </c>
-      <c r="HQ4" t="s">
-        <v>276</v>
-      </c>
-      <c r="HR4" t="s">
-        <v>276</v>
-      </c>
-      <c r="HS4">
+      <c r="IH4" t="s">
+        <v>294</v>
+      </c>
+      <c r="II4" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ4" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK4">
         <v>86400</v>
       </c>
-      <c r="HT4" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU4">
+      <c r="IL4" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM4">
         <v>86400</v>
       </c>
-      <c r="HV4" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW4">
-        <v>1</v>
-      </c>
-      <c r="HX4" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY4">
-        <v>1</v>
-      </c>
-      <c r="HZ4" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA4" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB4" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC4" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID4" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE4">
+      <c r="IN4" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO4">
+        <v>1</v>
+      </c>
+      <c r="IP4" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ4">
+        <v>1</v>
+      </c>
+      <c r="IR4" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS4" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT4" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU4" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV4" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW4">
         <v>86400</v>
       </c>
-      <c r="IF4">
+      <c r="IX4">
         <v>86400</v>
       </c>
-      <c r="IG4">
+      <c r="IY4">
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:241">
+    <row r="5" spans="1:259">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3896,7 +4238,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3908,13 +4250,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>4402000</v>
+        <v>3648000</v>
       </c>
       <c r="O5" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -3929,10 +4271,10 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -3944,7 +4286,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA5">
         <v>3</v>
@@ -3956,13 +4298,13 @@
         <v>20</v>
       </c>
       <c r="AD5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE5">
         <v>3</v>
       </c>
       <c r="AF5" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG5">
         <v>3</v>
@@ -3977,7 +4319,7 @@
         <v>6</v>
       </c>
       <c r="AM5" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -3992,10 +4334,10 @@
         <v>9</v>
       </c>
       <c r="AR5" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT5">
         <v>3</v>
@@ -4007,7 +4349,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX5">
         <v>3</v>
@@ -4019,25 +4361,34 @@
         <v>20</v>
       </c>
       <c r="BA5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB5">
         <v>3</v>
       </c>
       <c r="BC5" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD5">
         <v>3</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG5">
+        <v>19500000</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>283</v>
+      </c>
+      <c r="BI5">
+        <v>35</v>
       </c>
       <c r="BJ5" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK5">
         <v>1</v>
@@ -4052,10 +4403,10 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ5">
         <v>3</v>
@@ -4067,7 +4418,7 @@
         <v>20</v>
       </c>
       <c r="BT5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU5">
         <v>3</v>
@@ -4079,13 +4430,13 @@
         <v>20</v>
       </c>
       <c r="BX5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY5">
         <v>3</v>
       </c>
       <c r="BZ5" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA5">
         <v>0</v>
@@ -4094,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="CF5" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG5">
         <v>1</v>
@@ -4109,10 +4460,10 @@
         <v>9</v>
       </c>
       <c r="CK5" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM5">
         <v>3</v>
@@ -4124,7 +4475,7 @@
         <v>20</v>
       </c>
       <c r="CP5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ5">
         <v>3</v>
@@ -4136,13 +4487,13 @@
         <v>20</v>
       </c>
       <c r="CT5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU5">
         <v>3</v>
       </c>
       <c r="CV5" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW5">
         <v>3</v>
@@ -4154,22 +4505,22 @@
         <v>1</v>
       </c>
       <c r="CZ5">
-        <v>5700</v>
+        <v>4900</v>
       </c>
       <c r="DA5" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="DB5">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="DC5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DD5" t="b">
         <v>1</v>
       </c>
       <c r="DE5" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF5">
         <v>1</v>
@@ -4184,10 +4535,10 @@
         <v>9</v>
       </c>
       <c r="DJ5" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL5">
         <v>3</v>
@@ -4199,7 +4550,7 @@
         <v>20</v>
       </c>
       <c r="DO5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP5">
         <v>3</v>
@@ -4211,19 +4562,19 @@
         <v>20</v>
       </c>
       <c r="DS5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT5">
         <v>3</v>
       </c>
       <c r="DU5" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV5">
         <v>3</v>
       </c>
       <c r="DW5" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX5">
         <v>0</v>
@@ -4232,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED5">
         <v>1</v>
@@ -4247,10 +4598,10 @@
         <v>9</v>
       </c>
       <c r="EH5" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ5">
         <v>3</v>
@@ -4262,7 +4613,7 @@
         <v>20</v>
       </c>
       <c r="EM5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN5">
         <v>3</v>
@@ -4274,19 +4625,19 @@
         <v>20</v>
       </c>
       <c r="EQ5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER5">
         <v>3</v>
       </c>
       <c r="ES5" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET5">
         <v>3</v>
       </c>
       <c r="EU5" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV5">
         <v>0</v>
@@ -4295,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="FA5" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB5">
         <v>1</v>
@@ -4310,10 +4661,10 @@
         <v>9</v>
       </c>
       <c r="FF5" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH5">
         <v>3</v>
@@ -4325,7 +4676,7 @@
         <v>20</v>
       </c>
       <c r="FK5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL5">
         <v>3</v>
@@ -4337,135 +4688,252 @@
         <v>20</v>
       </c>
       <c r="FO5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP5">
         <v>3</v>
       </c>
       <c r="FQ5" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR5">
         <v>3</v>
       </c>
       <c r="FS5" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV5">
+        <v>9800</v>
+      </c>
+      <c r="FW5" t="s">
+        <v>295</v>
       </c>
       <c r="FX5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FZ5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="GA5">
+        <v>2</v>
+      </c>
+      <c r="GB5">
+        <v>9</v>
+      </c>
+      <c r="GC5" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD5" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE5">
+        <v>3</v>
+      </c>
+      <c r="GF5">
+        <v>20</v>
+      </c>
+      <c r="GG5">
+        <v>20</v>
+      </c>
+      <c r="GH5" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI5">
+        <v>3</v>
+      </c>
+      <c r="GJ5">
+        <v>20</v>
+      </c>
+      <c r="GK5">
+        <v>20</v>
+      </c>
+      <c r="GL5" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM5">
+        <v>3</v>
+      </c>
+      <c r="GN5" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO5">
+        <v>3</v>
+      </c>
+      <c r="GP5" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ5">
+        <v>1</v>
+      </c>
+      <c r="GR5">
+        <v>1</v>
       </c>
       <c r="GS5" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="GT5">
+        <v>50000</v>
+      </c>
+      <c r="GU5">
+        <v>7200</v>
+      </c>
+      <c r="GV5">
+        <v>7200</v>
+      </c>
+      <c r="GW5">
+        <v>50000</v>
+      </c>
+      <c r="GX5">
+        <v>0.9</v>
+      </c>
+      <c r="GY5">
+        <v>0.8</v>
+      </c>
+      <c r="GZ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="HA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="HK5" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL5">
         <v>0.05</v>
       </c>
-      <c r="GU5">
+      <c r="HM5">
         <v>0.5</v>
       </c>
-      <c r="GV5">
+      <c r="HN5">
         <v>0.8</v>
       </c>
-      <c r="GW5">
+      <c r="HO5">
         <v>8.5</v>
       </c>
-      <c r="GX5" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY5" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ5" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA5">
-        <v>0</v>
-      </c>
-      <c r="HB5">
-        <v>0</v>
-      </c>
-      <c r="HI5" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ5">
-        <v>0</v>
-      </c>
-      <c r="HK5">
-        <v>0</v>
-      </c>
       <c r="HP5" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="HQ5" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="HR5" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="HS5">
+        <v>1</v>
+      </c>
+      <c r="HT5">
+        <v>1</v>
+      </c>
+      <c r="HU5">
+        <v>3600</v>
+      </c>
+      <c r="HV5">
+        <v>3600</v>
+      </c>
+      <c r="HW5">
+        <v>0.95</v>
+      </c>
+      <c r="HX5">
+        <v>0.1</v>
+      </c>
+      <c r="HY5" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="IA5" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB5">
+        <v>1</v>
+      </c>
+      <c r="IC5">
+        <v>1</v>
+      </c>
+      <c r="ID5">
+        <v>9800</v>
+      </c>
+      <c r="IE5">
+        <v>19500</v>
+      </c>
+      <c r="IF5">
+        <v>0.95</v>
+      </c>
+      <c r="IG5">
+        <v>0.5</v>
+      </c>
+      <c r="IH5" t="s">
+        <v>294</v>
+      </c>
+      <c r="II5" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ5" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK5">
         <v>86400</v>
       </c>
-      <c r="HT5" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU5">
+      <c r="IL5" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM5">
         <v>86400</v>
       </c>
-      <c r="HV5" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW5">
-        <v>1</v>
-      </c>
-      <c r="HX5" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY5">
-        <v>1</v>
-      </c>
-      <c r="HZ5" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA5" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB5" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC5" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID5" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE5">
+      <c r="IN5" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO5">
+        <v>1</v>
+      </c>
+      <c r="IP5" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ5">
+        <v>1</v>
+      </c>
+      <c r="IR5" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS5" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT5" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU5" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV5" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW5">
         <v>86400</v>
       </c>
-      <c r="IF5">
+      <c r="IX5">
         <v>86400</v>
       </c>
-      <c r="IG5">
+      <c r="IY5">
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:241">
+    <row r="6" spans="1:259">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -4492,13 +4960,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>2959000</v>
+        <v>3125000</v>
       </c>
       <c r="O6" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="P6" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4513,10 +4981,10 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W6">
         <v>3</v>
@@ -4528,7 +4996,7 @@
         <v>20</v>
       </c>
       <c r="Z6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -4540,13 +5008,13 @@
         <v>20</v>
       </c>
       <c r="AD6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE6">
         <v>3</v>
       </c>
       <c r="AF6" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG6">
         <v>3</v>
@@ -4561,7 +5029,7 @@
         <v>6</v>
       </c>
       <c r="AM6" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN6">
         <v>1</v>
@@ -4576,10 +5044,10 @@
         <v>9</v>
       </c>
       <c r="AR6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT6">
         <v>3</v>
@@ -4591,7 +5059,7 @@
         <v>20</v>
       </c>
       <c r="AW6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX6">
         <v>3</v>
@@ -4603,25 +5071,34 @@
         <v>20</v>
       </c>
       <c r="BA6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB6">
         <v>3</v>
       </c>
       <c r="BC6" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD6">
         <v>3</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG6">
+        <v>5500000</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>284</v>
+      </c>
+      <c r="BI6">
+        <v>55</v>
       </c>
       <c r="BJ6" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK6">
         <v>1</v>
@@ -4636,10 +5113,10 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ6">
         <v>3</v>
@@ -4651,7 +5128,7 @@
         <v>20</v>
       </c>
       <c r="BT6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU6">
         <v>3</v>
@@ -4663,13 +5140,13 @@
         <v>20</v>
       </c>
       <c r="BX6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY6">
         <v>3</v>
       </c>
       <c r="BZ6" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA6">
         <v>0</v>
@@ -4678,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="CF6" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG6">
         <v>1</v>
@@ -4693,10 +5170,10 @@
         <v>9</v>
       </c>
       <c r="CK6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM6">
         <v>3</v>
@@ -4708,7 +5185,7 @@
         <v>20</v>
       </c>
       <c r="CP6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ6">
         <v>3</v>
@@ -4720,13 +5197,13 @@
         <v>20</v>
       </c>
       <c r="CT6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU6">
         <v>3</v>
       </c>
       <c r="CV6" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW6">
         <v>3</v>
@@ -4738,10 +5215,10 @@
         <v>1</v>
       </c>
       <c r="CZ6">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="DA6" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="DB6">
         <v>0</v>
@@ -4753,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="DE6" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF6">
         <v>1</v>
@@ -4768,10 +5245,10 @@
         <v>9</v>
       </c>
       <c r="DJ6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL6">
         <v>3</v>
@@ -4783,7 +5260,7 @@
         <v>20</v>
       </c>
       <c r="DO6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP6">
         <v>3</v>
@@ -4795,19 +5272,19 @@
         <v>20</v>
       </c>
       <c r="DS6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT6">
         <v>3</v>
       </c>
       <c r="DU6" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV6">
         <v>3</v>
       </c>
       <c r="DW6" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX6">
         <v>0</v>
@@ -4816,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED6">
         <v>1</v>
@@ -4831,10 +5308,10 @@
         <v>9</v>
       </c>
       <c r="EH6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ6">
         <v>3</v>
@@ -4846,7 +5323,7 @@
         <v>20</v>
       </c>
       <c r="EM6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN6">
         <v>3</v>
@@ -4858,19 +5335,19 @@
         <v>20</v>
       </c>
       <c r="EQ6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER6">
         <v>3</v>
       </c>
       <c r="ES6" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET6">
         <v>3</v>
       </c>
       <c r="EU6" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV6">
         <v>0</v>
@@ -4879,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="FA6" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB6">
         <v>1</v>
@@ -4894,10 +5371,10 @@
         <v>9</v>
       </c>
       <c r="FF6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH6">
         <v>3</v>
@@ -4909,7 +5386,7 @@
         <v>20</v>
       </c>
       <c r="FK6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL6">
         <v>3</v>
@@ -4921,28 +5398,34 @@
         <v>20</v>
       </c>
       <c r="FO6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP6">
         <v>3</v>
       </c>
       <c r="FQ6" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR6">
         <v>3</v>
       </c>
       <c r="FS6" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV6">
+        <v>2800</v>
+      </c>
+      <c r="FW6" t="s">
+        <v>296</v>
       </c>
       <c r="FX6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY6">
         <v>1</v>
@@ -4950,151 +5433,217 @@
       <c r="FZ6">
         <v>1</v>
       </c>
-      <c r="GA6" t="s">
-        <v>268</v>
+      <c r="GA6">
+        <v>2</v>
       </c>
       <c r="GB6">
-        <v>50000</v>
-      </c>
-      <c r="GC6">
-        <v>7200</v>
-      </c>
-      <c r="GD6">
-        <v>7200</v>
+        <v>9</v>
+      </c>
+      <c r="GC6" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD6" t="s">
+        <v>277</v>
       </c>
       <c r="GE6">
-        <v>50000</v>
+        <v>3</v>
       </c>
       <c r="GF6">
+        <v>20</v>
+      </c>
+      <c r="GG6">
+        <v>20</v>
+      </c>
+      <c r="GH6" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI6">
+        <v>3</v>
+      </c>
+      <c r="GJ6">
+        <v>20</v>
+      </c>
+      <c r="GK6">
+        <v>20</v>
+      </c>
+      <c r="GL6" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM6">
+        <v>3</v>
+      </c>
+      <c r="GN6" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO6">
+        <v>3</v>
+      </c>
+      <c r="GP6" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ6">
+        <v>1</v>
+      </c>
+      <c r="GR6">
+        <v>1</v>
+      </c>
+      <c r="GS6" t="s">
+        <v>300</v>
+      </c>
+      <c r="GT6">
+        <v>100000</v>
+      </c>
+      <c r="GU6">
+        <v>11000</v>
+      </c>
+      <c r="GV6">
+        <v>22000</v>
+      </c>
+      <c r="GW6">
+        <v>200000</v>
+      </c>
+      <c r="GX6">
         <v>0.9</v>
       </c>
-      <c r="GG6">
+      <c r="GY6">
         <v>0.8</v>
       </c>
-      <c r="GH6" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="GS6" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT6">
+      <c r="GZ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="HA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="HK6" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL6">
         <v>0.05</v>
       </c>
-      <c r="GU6">
+      <c r="HM6">
         <v>0.5</v>
       </c>
-      <c r="GV6">
+      <c r="HN6">
         <v>0.8</v>
       </c>
-      <c r="GW6">
+      <c r="HO6">
         <v>8.5</v>
       </c>
-      <c r="GX6" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY6" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ6" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA6">
-        <v>1</v>
-      </c>
-      <c r="HB6">
-        <v>1</v>
-      </c>
-      <c r="HC6">
-        <v>3000</v>
-      </c>
-      <c r="HD6">
-        <v>3000</v>
-      </c>
-      <c r="HE6">
+      <c r="HP6" t="s">
+        <v>304</v>
+      </c>
+      <c r="HQ6" t="s">
+        <v>305</v>
+      </c>
+      <c r="HR6" t="s">
+        <v>294</v>
+      </c>
+      <c r="HS6">
+        <v>1</v>
+      </c>
+      <c r="HT6">
+        <v>1</v>
+      </c>
+      <c r="HU6">
+        <v>3100</v>
+      </c>
+      <c r="HV6">
+        <v>3100</v>
+      </c>
+      <c r="HW6">
         <v>0.95</v>
       </c>
-      <c r="HF6">
+      <c r="HX6">
         <v>0.1</v>
       </c>
-      <c r="HG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH6" t="b">
-        <v>0</v>
-      </c>
-      <c r="HI6" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ6">
-        <v>0</v>
-      </c>
-      <c r="HK6">
-        <v>0</v>
-      </c>
-      <c r="HP6" t="s">
-        <v>267</v>
-      </c>
-      <c r="HQ6" t="s">
-        <v>276</v>
-      </c>
-      <c r="HR6" t="s">
-        <v>276</v>
-      </c>
-      <c r="HS6">
+      <c r="HY6" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="IA6" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB6">
+        <v>1</v>
+      </c>
+      <c r="IC6">
+        <v>1</v>
+      </c>
+      <c r="ID6">
+        <v>2800</v>
+      </c>
+      <c r="IE6">
+        <v>5500</v>
+      </c>
+      <c r="IF6">
+        <v>0.95</v>
+      </c>
+      <c r="IG6">
+        <v>0.5</v>
+      </c>
+      <c r="IH6" t="s">
+        <v>294</v>
+      </c>
+      <c r="II6" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ6" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK6">
         <v>86400</v>
       </c>
-      <c r="HT6" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU6">
+      <c r="IL6" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM6">
         <v>86400</v>
       </c>
-      <c r="HV6" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW6">
-        <v>1</v>
-      </c>
-      <c r="HX6" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY6">
-        <v>1</v>
-      </c>
-      <c r="HZ6" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA6" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB6" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC6" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID6" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE6">
+      <c r="IN6" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO6">
+        <v>1</v>
+      </c>
+      <c r="IP6" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ6">
+        <v>1</v>
+      </c>
+      <c r="IR6" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS6" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT6" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU6" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV6" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW6">
         <v>86400</v>
       </c>
-      <c r="IF6">
+      <c r="IX6">
         <v>86400</v>
       </c>
-      <c r="IG6">
+      <c r="IY6">
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:241">
+    <row r="7" spans="1:259">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -5121,13 +5670,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3296000</v>
+        <v>3648000</v>
       </c>
       <c r="O7" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="P7" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -5142,10 +5691,10 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W7">
         <v>3</v>
@@ -5157,7 +5706,7 @@
         <v>20</v>
       </c>
       <c r="Z7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA7">
         <v>3</v>
@@ -5169,13 +5718,13 @@
         <v>20</v>
       </c>
       <c r="AD7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE7">
         <v>3</v>
       </c>
       <c r="AF7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG7">
         <v>3</v>
@@ -5190,7 +5739,7 @@
         <v>6</v>
       </c>
       <c r="AM7" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -5205,10 +5754,10 @@
         <v>9</v>
       </c>
       <c r="AR7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT7">
         <v>3</v>
@@ -5220,7 +5769,7 @@
         <v>20</v>
       </c>
       <c r="AW7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX7">
         <v>3</v>
@@ -5232,25 +5781,34 @@
         <v>20</v>
       </c>
       <c r="BA7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB7">
         <v>3</v>
       </c>
       <c r="BC7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD7">
         <v>3</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG7">
+        <v>19500000</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>283</v>
+      </c>
+      <c r="BI7">
+        <v>55</v>
       </c>
       <c r="BJ7" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK7">
         <v>1</v>
@@ -5265,10 +5823,10 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ7">
         <v>3</v>
@@ -5280,7 +5838,7 @@
         <v>20</v>
       </c>
       <c r="BT7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU7">
         <v>3</v>
@@ -5292,13 +5850,13 @@
         <v>20</v>
       </c>
       <c r="BX7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY7">
         <v>3</v>
       </c>
       <c r="BZ7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA7">
         <v>0</v>
@@ -5307,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="CF7" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG7">
         <v>1</v>
@@ -5322,10 +5880,10 @@
         <v>9</v>
       </c>
       <c r="CK7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM7">
         <v>3</v>
@@ -5337,7 +5895,7 @@
         <v>20</v>
       </c>
       <c r="CP7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ7">
         <v>3</v>
@@ -5349,13 +5907,13 @@
         <v>20</v>
       </c>
       <c r="CT7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU7">
         <v>3</v>
       </c>
       <c r="CV7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW7">
         <v>3</v>
@@ -5367,10 +5925,10 @@
         <v>1</v>
       </c>
       <c r="CZ7">
-        <v>5000</v>
+        <v>4400</v>
       </c>
       <c r="DA7" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="DB7">
         <v>0</v>
@@ -5382,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF7">
         <v>1</v>
@@ -5397,10 +5955,10 @@
         <v>9</v>
       </c>
       <c r="DJ7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL7">
         <v>3</v>
@@ -5412,7 +5970,7 @@
         <v>20</v>
       </c>
       <c r="DO7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP7">
         <v>3</v>
@@ -5424,19 +5982,19 @@
         <v>20</v>
       </c>
       <c r="DS7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT7">
         <v>3</v>
       </c>
       <c r="DU7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV7">
         <v>3</v>
       </c>
       <c r="DW7" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX7">
         <v>0</v>
@@ -5445,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED7">
         <v>1</v>
@@ -5460,10 +6018,10 @@
         <v>9</v>
       </c>
       <c r="EH7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ7">
         <v>3</v>
@@ -5475,7 +6033,7 @@
         <v>20</v>
       </c>
       <c r="EM7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN7">
         <v>3</v>
@@ -5487,19 +6045,19 @@
         <v>20</v>
       </c>
       <c r="EQ7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER7">
         <v>3</v>
       </c>
       <c r="ES7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET7">
         <v>3</v>
       </c>
       <c r="EU7" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV7">
         <v>0</v>
@@ -5508,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="FA7" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB7">
         <v>1</v>
@@ -5523,10 +6081,10 @@
         <v>9</v>
       </c>
       <c r="FF7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH7">
         <v>3</v>
@@ -5538,7 +6096,7 @@
         <v>20</v>
       </c>
       <c r="FK7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL7">
         <v>3</v>
@@ -5550,28 +6108,34 @@
         <v>20</v>
       </c>
       <c r="FO7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP7">
         <v>3</v>
       </c>
       <c r="FQ7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR7">
         <v>3</v>
       </c>
       <c r="FS7" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV7">
+        <v>9800</v>
+      </c>
+      <c r="FW7" t="s">
+        <v>295</v>
       </c>
       <c r="FX7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY7">
         <v>1</v>
@@ -5579,157 +6143,196 @@
       <c r="FZ7">
         <v>1</v>
       </c>
-      <c r="GA7" t="s">
-        <v>271</v>
+      <c r="GA7">
+        <v>2</v>
       </c>
       <c r="GB7">
-        <v>75000</v>
-      </c>
-      <c r="GC7">
-        <v>7200</v>
-      </c>
-      <c r="GD7">
-        <v>11000</v>
+        <v>9</v>
+      </c>
+      <c r="GC7" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD7" t="s">
+        <v>277</v>
       </c>
       <c r="GE7">
-        <v>100000</v>
+        <v>3</v>
       </c>
       <c r="GF7">
-        <v>0.9</v>
+        <v>20</v>
       </c>
       <c r="GG7">
+        <v>20</v>
+      </c>
+      <c r="GH7" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI7">
+        <v>3</v>
+      </c>
+      <c r="GJ7">
+        <v>20</v>
+      </c>
+      <c r="GK7">
+        <v>20</v>
+      </c>
+      <c r="GL7" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM7">
+        <v>3</v>
+      </c>
+      <c r="GN7" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO7">
+        <v>3</v>
+      </c>
+      <c r="GP7" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ7">
+        <v>0</v>
+      </c>
+      <c r="GR7">
+        <v>0</v>
+      </c>
+      <c r="HK7" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL7">
+        <v>0.05</v>
+      </c>
+      <c r="HM7">
+        <v>0.5</v>
+      </c>
+      <c r="HN7">
         <v>0.8</v>
       </c>
-      <c r="GH7" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="GS7" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT7">
-        <v>0.05</v>
-      </c>
-      <c r="GU7">
+      <c r="HO7">
+        <v>8.5</v>
+      </c>
+      <c r="HP7" t="s">
+        <v>304</v>
+      </c>
+      <c r="HQ7" t="s">
+        <v>305</v>
+      </c>
+      <c r="HR7" t="s">
+        <v>294</v>
+      </c>
+      <c r="HS7">
+        <v>1</v>
+      </c>
+      <c r="HT7">
+        <v>1</v>
+      </c>
+      <c r="HU7">
+        <v>3600</v>
+      </c>
+      <c r="HV7">
+        <v>3600</v>
+      </c>
+      <c r="HW7">
+        <v>0.95</v>
+      </c>
+      <c r="HX7">
+        <v>0.1</v>
+      </c>
+      <c r="HY7" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="IA7" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB7">
+        <v>1</v>
+      </c>
+      <c r="IC7">
+        <v>1</v>
+      </c>
+      <c r="ID7">
+        <v>9800</v>
+      </c>
+      <c r="IE7">
+        <v>19500</v>
+      </c>
+      <c r="IF7">
+        <v>0.95</v>
+      </c>
+      <c r="IG7">
         <v>0.5</v>
       </c>
-      <c r="GV7">
-        <v>0.8</v>
-      </c>
-      <c r="GW7">
-        <v>8.5</v>
-      </c>
-      <c r="GX7" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY7" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ7" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA7">
-        <v>1</v>
-      </c>
-      <c r="HB7">
-        <v>1</v>
-      </c>
-      <c r="HC7">
-        <v>3300</v>
-      </c>
-      <c r="HD7">
-        <v>3300</v>
-      </c>
-      <c r="HE7">
-        <v>0.95</v>
-      </c>
-      <c r="HF7">
-        <v>0.1</v>
-      </c>
-      <c r="HG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH7" t="b">
-        <v>0</v>
-      </c>
-      <c r="HI7" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ7">
-        <v>0</v>
-      </c>
-      <c r="HK7">
-        <v>0</v>
-      </c>
-      <c r="HP7" t="s">
-        <v>267</v>
-      </c>
-      <c r="HQ7" t="s">
-        <v>276</v>
-      </c>
-      <c r="HR7" t="s">
-        <v>276</v>
-      </c>
-      <c r="HS7">
+      <c r="IH7" t="s">
+        <v>294</v>
+      </c>
+      <c r="II7" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ7" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK7">
         <v>86400</v>
       </c>
-      <c r="HT7" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU7">
+      <c r="IL7" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM7">
         <v>86400</v>
       </c>
-      <c r="HV7" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW7">
-        <v>1</v>
-      </c>
-      <c r="HX7" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY7">
-        <v>1</v>
-      </c>
-      <c r="HZ7" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA7" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB7" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC7" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID7" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE7">
+      <c r="IN7" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO7">
+        <v>1</v>
+      </c>
+      <c r="IP7" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ7">
+        <v>1</v>
+      </c>
+      <c r="IR7" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS7" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT7" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU7" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV7" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW7">
         <v>86400</v>
       </c>
-      <c r="IF7">
+      <c r="IX7">
         <v>86400</v>
       </c>
-      <c r="IG7">
+      <c r="IY7">
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:241">
+    <row r="8" spans="1:259">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -5738,7 +6341,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -5753,10 +6356,10 @@
         <v>3125000</v>
       </c>
       <c r="O8" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="P8" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -5771,10 +6374,10 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W8">
         <v>3</v>
@@ -5786,7 +6389,7 @@
         <v>20</v>
       </c>
       <c r="Z8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA8">
         <v>3</v>
@@ -5798,13 +6401,13 @@
         <v>20</v>
       </c>
       <c r="AD8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE8">
         <v>3</v>
       </c>
       <c r="AF8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG8">
         <v>3</v>
@@ -5819,7 +6422,7 @@
         <v>6</v>
       </c>
       <c r="AM8" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN8">
         <v>1</v>
@@ -5834,10 +6437,10 @@
         <v>9</v>
       </c>
       <c r="AR8" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT8">
         <v>3</v>
@@ -5849,7 +6452,7 @@
         <v>20</v>
       </c>
       <c r="AW8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX8">
         <v>3</v>
@@ -5861,25 +6464,34 @@
         <v>20</v>
       </c>
       <c r="BA8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB8">
         <v>3</v>
       </c>
       <c r="BC8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD8">
         <v>3</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG8">
+        <v>19500000</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>285</v>
+      </c>
+      <c r="BI8">
+        <v>55</v>
       </c>
       <c r="BJ8" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK8">
         <v>1</v>
@@ -5894,10 +6506,10 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ8">
         <v>3</v>
@@ -5909,7 +6521,7 @@
         <v>20</v>
       </c>
       <c r="BT8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU8">
         <v>3</v>
@@ -5921,13 +6533,13 @@
         <v>20</v>
       </c>
       <c r="BX8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY8">
         <v>3</v>
       </c>
       <c r="BZ8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA8">
         <v>0</v>
@@ -5936,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="CF8" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG8">
         <v>1</v>
@@ -5951,10 +6563,10 @@
         <v>9</v>
       </c>
       <c r="CK8" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM8">
         <v>3</v>
@@ -5966,7 +6578,7 @@
         <v>20</v>
       </c>
       <c r="CP8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ8">
         <v>3</v>
@@ -5978,25 +6590,40 @@
         <v>20</v>
       </c>
       <c r="CT8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU8">
         <v>3</v>
       </c>
       <c r="CV8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW8">
         <v>3</v>
       </c>
       <c r="CX8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CZ8">
+        <v>5300</v>
+      </c>
+      <c r="DA8" t="s">
+        <v>291</v>
+      </c>
+      <c r="DB8">
+        <v>-20</v>
+      </c>
+      <c r="DC8">
+        <v>50</v>
+      </c>
+      <c r="DD8" t="b">
+        <v>1</v>
       </c>
       <c r="DE8" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF8">
         <v>1</v>
@@ -6011,10 +6638,10 @@
         <v>9</v>
       </c>
       <c r="DJ8" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL8">
         <v>3</v>
@@ -6026,7 +6653,7 @@
         <v>20</v>
       </c>
       <c r="DO8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP8">
         <v>3</v>
@@ -6038,19 +6665,19 @@
         <v>20</v>
       </c>
       <c r="DS8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT8">
         <v>3</v>
       </c>
       <c r="DU8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV8">
         <v>3</v>
       </c>
       <c r="DW8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX8">
         <v>0</v>
@@ -6059,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED8">
         <v>1</v>
@@ -6074,10 +6701,10 @@
         <v>9</v>
       </c>
       <c r="EH8" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ8">
         <v>3</v>
@@ -6089,7 +6716,7 @@
         <v>20</v>
       </c>
       <c r="EM8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN8">
         <v>3</v>
@@ -6101,19 +6728,19 @@
         <v>20</v>
       </c>
       <c r="EQ8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER8">
         <v>3</v>
       </c>
       <c r="ES8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET8">
         <v>3</v>
       </c>
       <c r="EU8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV8">
         <v>0</v>
@@ -6122,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="FA8" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB8">
         <v>1</v>
@@ -6137,10 +6764,10 @@
         <v>9</v>
       </c>
       <c r="FF8" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH8">
         <v>3</v>
@@ -6152,7 +6779,7 @@
         <v>20</v>
       </c>
       <c r="FK8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL8">
         <v>3</v>
@@ -6164,141 +6791,258 @@
         <v>20</v>
       </c>
       <c r="FO8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP8">
         <v>3</v>
       </c>
       <c r="FQ8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR8">
         <v>3</v>
       </c>
       <c r="FS8" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV8">
+        <v>9800</v>
+      </c>
+      <c r="FW8" t="s">
+        <v>295</v>
       </c>
       <c r="FX8" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FZ8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="GA8">
+        <v>2</v>
+      </c>
+      <c r="GB8">
+        <v>9</v>
+      </c>
+      <c r="GC8" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD8" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE8">
+        <v>3</v>
+      </c>
+      <c r="GF8">
+        <v>20</v>
+      </c>
+      <c r="GG8">
+        <v>20</v>
+      </c>
+      <c r="GH8" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI8">
+        <v>3</v>
+      </c>
+      <c r="GJ8">
+        <v>20</v>
+      </c>
+      <c r="GK8">
+        <v>20</v>
+      </c>
+      <c r="GL8" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM8">
+        <v>3</v>
+      </c>
+      <c r="GN8" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO8">
+        <v>3</v>
+      </c>
+      <c r="GP8" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ8">
+        <v>1</v>
+      </c>
+      <c r="GR8">
+        <v>1</v>
       </c>
       <c r="GS8" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="GT8">
+        <v>50000</v>
+      </c>
+      <c r="GU8">
+        <v>7200</v>
+      </c>
+      <c r="GV8">
+        <v>7200</v>
+      </c>
+      <c r="GW8">
+        <v>50000</v>
+      </c>
+      <c r="GX8">
+        <v>0.9</v>
+      </c>
+      <c r="GY8">
+        <v>0.8</v>
+      </c>
+      <c r="GZ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="HA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="HK8" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL8">
         <v>0.05</v>
       </c>
-      <c r="GU8">
+      <c r="HM8">
         <v>0.5</v>
       </c>
-      <c r="GV8">
+      <c r="HN8">
         <v>0.8</v>
       </c>
-      <c r="GW8">
+      <c r="HO8">
         <v>8.5</v>
       </c>
-      <c r="GX8" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY8" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ8" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA8">
-        <v>0</v>
-      </c>
-      <c r="HB8">
-        <v>0</v>
-      </c>
-      <c r="HI8" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ8">
-        <v>0</v>
-      </c>
-      <c r="HK8">
-        <v>0</v>
-      </c>
       <c r="HP8" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="HQ8" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="HR8" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="HS8">
+        <v>1</v>
+      </c>
+      <c r="HT8">
+        <v>1</v>
+      </c>
+      <c r="HU8">
+        <v>3100</v>
+      </c>
+      <c r="HV8">
+        <v>3100</v>
+      </c>
+      <c r="HW8">
+        <v>0.95</v>
+      </c>
+      <c r="HX8">
+        <v>0.1</v>
+      </c>
+      <c r="HY8" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="IA8" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB8">
+        <v>1</v>
+      </c>
+      <c r="IC8">
+        <v>1</v>
+      </c>
+      <c r="ID8">
+        <v>9800</v>
+      </c>
+      <c r="IE8">
+        <v>19500</v>
+      </c>
+      <c r="IF8">
+        <v>0.95</v>
+      </c>
+      <c r="IG8">
+        <v>0.5</v>
+      </c>
+      <c r="IH8" t="s">
+        <v>294</v>
+      </c>
+      <c r="II8" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ8" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK8">
         <v>86400</v>
       </c>
-      <c r="HT8" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU8">
+      <c r="IL8" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM8">
         <v>86400</v>
       </c>
-      <c r="HV8" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW8">
-        <v>1</v>
-      </c>
-      <c r="HX8" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY8">
-        <v>1</v>
-      </c>
-      <c r="HZ8" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA8" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB8" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC8" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID8" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE8">
+      <c r="IN8" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO8">
+        <v>1</v>
+      </c>
+      <c r="IP8" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ8">
+        <v>1</v>
+      </c>
+      <c r="IR8" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS8" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT8" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU8" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV8" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW8">
         <v>86400</v>
       </c>
-      <c r="IF8">
+      <c r="IX8">
         <v>86400</v>
       </c>
-      <c r="IG8">
+      <c r="IY8">
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:241">
+    <row r="9" spans="1:259">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -6307,7 +7051,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -6319,13 +7063,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3564000</v>
+        <v>5527000</v>
       </c>
       <c r="O9" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="P9" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -6340,10 +7084,10 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W9">
         <v>3</v>
@@ -6355,7 +7099,7 @@
         <v>20</v>
       </c>
       <c r="Z9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA9">
         <v>3</v>
@@ -6367,13 +7111,13 @@
         <v>20</v>
       </c>
       <c r="AD9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE9">
         <v>3</v>
       </c>
       <c r="AF9" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG9">
         <v>3</v>
@@ -6388,7 +7132,7 @@
         <v>6</v>
       </c>
       <c r="AM9" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN9">
         <v>1</v>
@@ -6403,10 +7147,10 @@
         <v>9</v>
       </c>
       <c r="AR9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT9">
         <v>3</v>
@@ -6418,7 +7162,7 @@
         <v>20</v>
       </c>
       <c r="AW9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX9">
         <v>3</v>
@@ -6430,25 +7174,34 @@
         <v>20</v>
       </c>
       <c r="BA9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB9">
         <v>3</v>
       </c>
       <c r="BC9" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD9">
         <v>3</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG9">
+        <v>5500000</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>286</v>
+      </c>
+      <c r="BI9">
+        <v>55</v>
       </c>
       <c r="BJ9" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK9">
         <v>1</v>
@@ -6463,10 +7216,10 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ9">
         <v>3</v>
@@ -6478,7 +7231,7 @@
         <v>20</v>
       </c>
       <c r="BT9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU9">
         <v>3</v>
@@ -6490,13 +7243,13 @@
         <v>20</v>
       </c>
       <c r="BX9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY9">
         <v>3</v>
       </c>
       <c r="BZ9" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA9">
         <v>0</v>
@@ -6505,7 +7258,7 @@
         <v>0</v>
       </c>
       <c r="CF9" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG9">
         <v>1</v>
@@ -6520,10 +7273,10 @@
         <v>9</v>
       </c>
       <c r="CK9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM9">
         <v>3</v>
@@ -6535,7 +7288,7 @@
         <v>20</v>
       </c>
       <c r="CP9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ9">
         <v>3</v>
@@ -6547,13 +7300,13 @@
         <v>20</v>
       </c>
       <c r="CT9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU9">
         <v>3</v>
       </c>
       <c r="CV9" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW9">
         <v>3</v>
@@ -6565,10 +7318,10 @@
         <v>1</v>
       </c>
       <c r="CZ9">
-        <v>6200</v>
+        <v>8700</v>
       </c>
       <c r="DA9" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="DB9">
         <v>0</v>
@@ -6580,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="DE9" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF9">
         <v>1</v>
@@ -6595,10 +7348,10 @@
         <v>9</v>
       </c>
       <c r="DJ9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL9">
         <v>3</v>
@@ -6610,7 +7363,7 @@
         <v>20</v>
       </c>
       <c r="DO9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP9">
         <v>3</v>
@@ -6622,19 +7375,19 @@
         <v>20</v>
       </c>
       <c r="DS9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT9">
         <v>3</v>
       </c>
       <c r="DU9" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV9">
         <v>3</v>
       </c>
       <c r="DW9" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX9">
         <v>0</v>
@@ -6643,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED9">
         <v>1</v>
@@ -6658,10 +7411,10 @@
         <v>9</v>
       </c>
       <c r="EH9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ9">
         <v>3</v>
@@ -6673,7 +7426,7 @@
         <v>20</v>
       </c>
       <c r="EM9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN9">
         <v>3</v>
@@ -6685,19 +7438,19 @@
         <v>20</v>
       </c>
       <c r="EQ9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER9">
         <v>3</v>
       </c>
       <c r="ES9" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET9">
         <v>3</v>
       </c>
       <c r="EU9" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV9">
         <v>0</v>
@@ -6706,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="FA9" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB9">
         <v>1</v>
@@ -6721,10 +7474,10 @@
         <v>9</v>
       </c>
       <c r="FF9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH9">
         <v>3</v>
@@ -6736,7 +7489,7 @@
         <v>20</v>
       </c>
       <c r="FK9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL9">
         <v>3</v>
@@ -6748,159 +7501,231 @@
         <v>20</v>
       </c>
       <c r="FO9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP9">
         <v>3</v>
       </c>
       <c r="FQ9" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR9">
         <v>3</v>
       </c>
       <c r="FS9" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV9">
+        <v>2800</v>
+      </c>
+      <c r="FW9" t="s">
+        <v>296</v>
       </c>
       <c r="FX9" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FZ9">
-        <v>0</v>
-      </c>
-      <c r="GS9" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT9">
+        <v>1</v>
+      </c>
+      <c r="GA9">
+        <v>2</v>
+      </c>
+      <c r="GB9">
+        <v>9</v>
+      </c>
+      <c r="GC9" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD9" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE9">
+        <v>3</v>
+      </c>
+      <c r="GF9">
+        <v>20</v>
+      </c>
+      <c r="GG9">
+        <v>20</v>
+      </c>
+      <c r="GH9" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI9">
+        <v>3</v>
+      </c>
+      <c r="GJ9">
+        <v>20</v>
+      </c>
+      <c r="GK9">
+        <v>20</v>
+      </c>
+      <c r="GL9" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM9">
+        <v>3</v>
+      </c>
+      <c r="GN9" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO9">
+        <v>3</v>
+      </c>
+      <c r="GP9" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ9">
+        <v>0</v>
+      </c>
+      <c r="GR9">
+        <v>0</v>
+      </c>
+      <c r="HK9" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL9">
         <v>0.05</v>
       </c>
-      <c r="GU9">
+      <c r="HM9">
         <v>0.5</v>
       </c>
-      <c r="GV9">
+      <c r="HN9">
         <v>0.8</v>
       </c>
-      <c r="GW9">
+      <c r="HO9">
         <v>8.5</v>
       </c>
-      <c r="GX9" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY9" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ9" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA9">
-        <v>1</v>
-      </c>
-      <c r="HB9">
-        <v>1</v>
-      </c>
-      <c r="HC9">
+      <c r="HP9" t="s">
+        <v>304</v>
+      </c>
+      <c r="HQ9" t="s">
+        <v>305</v>
+      </c>
+      <c r="HR9" t="s">
+        <v>294</v>
+      </c>
+      <c r="HS9">
+        <v>1</v>
+      </c>
+      <c r="HT9">
+        <v>1</v>
+      </c>
+      <c r="HU9">
+        <v>5500</v>
+      </c>
+      <c r="HV9">
+        <v>5500</v>
+      </c>
+      <c r="HW9">
+        <v>0.95</v>
+      </c>
+      <c r="HX9">
+        <v>0.1</v>
+      </c>
+      <c r="HY9" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="IA9" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB9">
+        <v>1</v>
+      </c>
+      <c r="IC9">
+        <v>1</v>
+      </c>
+      <c r="ID9">
+        <v>2800</v>
+      </c>
+      <c r="IE9">
+        <v>5500</v>
+      </c>
+      <c r="IF9">
+        <v>0.95</v>
+      </c>
+      <c r="IG9">
+        <v>0.5</v>
+      </c>
+      <c r="IH9" t="s">
+        <v>294</v>
+      </c>
+      <c r="II9" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ9" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK9">
+        <v>86400</v>
+      </c>
+      <c r="IL9" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM9">
+        <v>86400</v>
+      </c>
+      <c r="IN9" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO9">
+        <v>1</v>
+      </c>
+      <c r="IP9" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ9">
+        <v>1</v>
+      </c>
+      <c r="IR9" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS9" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT9" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU9" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV9" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW9">
+        <v>86400</v>
+      </c>
+      <c r="IX9">
+        <v>86400</v>
+      </c>
+      <c r="IY9">
         <v>3600</v>
       </c>
-      <c r="HD9">
-        <v>3600</v>
-      </c>
-      <c r="HE9">
-        <v>0.95</v>
-      </c>
-      <c r="HF9">
-        <v>0.1</v>
-      </c>
-      <c r="HG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH9" t="b">
-        <v>0</v>
-      </c>
-      <c r="HI9" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ9">
-        <v>0</v>
-      </c>
-      <c r="HK9">
-        <v>0</v>
-      </c>
-      <c r="HP9" t="s">
-        <v>267</v>
-      </c>
-      <c r="HQ9" t="s">
-        <v>276</v>
-      </c>
-      <c r="HR9" t="s">
-        <v>276</v>
-      </c>
-      <c r="HS9">
-        <v>86400</v>
-      </c>
-      <c r="HT9" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU9">
-        <v>86400</v>
-      </c>
-      <c r="HV9" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW9">
-        <v>1</v>
-      </c>
-      <c r="HX9" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY9">
-        <v>1</v>
-      </c>
-      <c r="HZ9" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA9" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB9" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC9" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID9" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE9">
-        <v>86400</v>
-      </c>
-      <c r="IF9">
-        <v>86400</v>
-      </c>
-      <c r="IG9">
-        <v>3600</v>
-      </c>
     </row>
-    <row r="10" spans="1:241">
+    <row r="10" spans="1:259">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -6909,7 +7734,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -6921,13 +7746,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>2687000</v>
+        <v>4402000</v>
       </c>
       <c r="O10" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="P10" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -6942,10 +7767,10 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W10">
         <v>3</v>
@@ -6957,7 +7782,7 @@
         <v>20</v>
       </c>
       <c r="Z10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA10">
         <v>3</v>
@@ -6969,13 +7794,13 @@
         <v>20</v>
       </c>
       <c r="AD10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE10">
         <v>3</v>
       </c>
       <c r="AF10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG10">
         <v>3</v>
@@ -6990,7 +7815,7 @@
         <v>6</v>
       </c>
       <c r="AM10" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN10">
         <v>1</v>
@@ -7005,10 +7830,10 @@
         <v>9</v>
       </c>
       <c r="AR10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT10">
         <v>3</v>
@@ -7020,7 +7845,7 @@
         <v>20</v>
       </c>
       <c r="AW10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX10">
         <v>3</v>
@@ -7032,25 +7857,34 @@
         <v>20</v>
       </c>
       <c r="BA10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB10">
         <v>3</v>
       </c>
       <c r="BC10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD10">
         <v>3</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG10">
+        <v>5500000</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>287</v>
+      </c>
+      <c r="BI10">
+        <v>35</v>
       </c>
       <c r="BJ10" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK10">
         <v>1</v>
@@ -7065,10 +7899,10 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ10">
         <v>3</v>
@@ -7080,7 +7914,7 @@
         <v>20</v>
       </c>
       <c r="BT10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU10">
         <v>3</v>
@@ -7092,13 +7926,13 @@
         <v>20</v>
       </c>
       <c r="BX10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY10">
         <v>3</v>
       </c>
       <c r="BZ10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA10">
         <v>0</v>
@@ -7107,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="CF10" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG10">
         <v>1</v>
@@ -7122,10 +7956,10 @@
         <v>9</v>
       </c>
       <c r="CK10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM10">
         <v>3</v>
@@ -7137,7 +7971,7 @@
         <v>20</v>
       </c>
       <c r="CP10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ10">
         <v>3</v>
@@ -7149,40 +7983,25 @@
         <v>20</v>
       </c>
       <c r="CT10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU10">
         <v>3</v>
       </c>
       <c r="CV10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW10">
         <v>3</v>
       </c>
       <c r="CX10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY10">
-        <v>1</v>
-      </c>
-      <c r="CZ10">
-        <v>4200</v>
-      </c>
-      <c r="DA10" t="s">
-        <v>264</v>
-      </c>
-      <c r="DB10">
-        <v>-20</v>
-      </c>
-      <c r="DC10">
-        <v>50</v>
-      </c>
-      <c r="DD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF10">
         <v>1</v>
@@ -7197,10 +8016,10 @@
         <v>9</v>
       </c>
       <c r="DJ10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL10">
         <v>3</v>
@@ -7212,7 +8031,7 @@
         <v>20</v>
       </c>
       <c r="DO10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP10">
         <v>3</v>
@@ -7224,19 +8043,19 @@
         <v>20</v>
       </c>
       <c r="DS10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT10">
         <v>3</v>
       </c>
       <c r="DU10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV10">
         <v>3</v>
       </c>
       <c r="DW10" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX10">
         <v>0</v>
@@ -7245,7 +8064,7 @@
         <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED10">
         <v>1</v>
@@ -7260,10 +8079,10 @@
         <v>9</v>
       </c>
       <c r="EH10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ10">
         <v>3</v>
@@ -7275,7 +8094,7 @@
         <v>20</v>
       </c>
       <c r="EM10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN10">
         <v>3</v>
@@ -7287,19 +8106,19 @@
         <v>20</v>
       </c>
       <c r="EQ10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER10">
         <v>3</v>
       </c>
       <c r="ES10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET10">
         <v>3</v>
       </c>
       <c r="EU10" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV10">
         <v>0</v>
@@ -7308,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="FA10" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB10">
         <v>1</v>
@@ -7323,10 +8142,10 @@
         <v>9</v>
       </c>
       <c r="FF10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH10">
         <v>3</v>
@@ -7338,7 +8157,7 @@
         <v>20</v>
       </c>
       <c r="FK10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL10">
         <v>3</v>
@@ -7350,159 +8169,213 @@
         <v>20</v>
       </c>
       <c r="FO10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP10">
         <v>3</v>
       </c>
       <c r="FQ10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR10">
         <v>3</v>
       </c>
       <c r="FS10" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV10">
+        <v>2800</v>
+      </c>
+      <c r="FW10" t="s">
+        <v>295</v>
       </c>
       <c r="FX10" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FZ10">
-        <v>0</v>
-      </c>
-      <c r="GS10" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT10">
+        <v>1</v>
+      </c>
+      <c r="GA10">
+        <v>2</v>
+      </c>
+      <c r="GB10">
+        <v>9</v>
+      </c>
+      <c r="GC10" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD10" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE10">
+        <v>3</v>
+      </c>
+      <c r="GF10">
+        <v>20</v>
+      </c>
+      <c r="GG10">
+        <v>20</v>
+      </c>
+      <c r="GH10" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI10">
+        <v>3</v>
+      </c>
+      <c r="GJ10">
+        <v>20</v>
+      </c>
+      <c r="GK10">
+        <v>20</v>
+      </c>
+      <c r="GL10" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM10">
+        <v>3</v>
+      </c>
+      <c r="GN10" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO10">
+        <v>3</v>
+      </c>
+      <c r="GP10" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ10">
+        <v>0</v>
+      </c>
+      <c r="GR10">
+        <v>0</v>
+      </c>
+      <c r="HK10" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL10">
         <v>0.05</v>
       </c>
-      <c r="GU10">
+      <c r="HM10">
         <v>0.5</v>
       </c>
-      <c r="GV10">
+      <c r="HN10">
         <v>0.8</v>
       </c>
-      <c r="GW10">
+      <c r="HO10">
         <v>8.5</v>
       </c>
-      <c r="GX10" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY10" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ10" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA10">
-        <v>1</v>
-      </c>
-      <c r="HB10">
-        <v>1</v>
-      </c>
-      <c r="HC10">
-        <v>2700</v>
-      </c>
-      <c r="HD10">
-        <v>2700</v>
-      </c>
-      <c r="HE10">
+      <c r="HP10" t="s">
+        <v>304</v>
+      </c>
+      <c r="HQ10" t="s">
+        <v>305</v>
+      </c>
+      <c r="HR10" t="s">
+        <v>294</v>
+      </c>
+      <c r="HS10">
+        <v>0</v>
+      </c>
+      <c r="HT10">
+        <v>0</v>
+      </c>
+      <c r="IA10" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB10">
+        <v>1</v>
+      </c>
+      <c r="IC10">
+        <v>1</v>
+      </c>
+      <c r="ID10">
+        <v>2800</v>
+      </c>
+      <c r="IE10">
+        <v>5500</v>
+      </c>
+      <c r="IF10">
         <v>0.95</v>
       </c>
-      <c r="HF10">
-        <v>0.1</v>
-      </c>
-      <c r="HG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH10" t="b">
-        <v>0</v>
-      </c>
-      <c r="HI10" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ10">
-        <v>0</v>
-      </c>
-      <c r="HK10">
-        <v>0</v>
-      </c>
-      <c r="HP10" t="s">
-        <v>267</v>
-      </c>
-      <c r="HQ10" t="s">
-        <v>276</v>
-      </c>
-      <c r="HR10" t="s">
-        <v>276</v>
-      </c>
-      <c r="HS10">
+      <c r="IG10">
+        <v>0.5</v>
+      </c>
+      <c r="IH10" t="s">
+        <v>294</v>
+      </c>
+      <c r="II10" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ10" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK10">
         <v>86400</v>
       </c>
-      <c r="HT10" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU10">
+      <c r="IL10" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM10">
         <v>86400</v>
       </c>
-      <c r="HV10" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW10">
-        <v>1</v>
-      </c>
-      <c r="HX10" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY10">
-        <v>1</v>
-      </c>
-      <c r="HZ10" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA10" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB10" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC10" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID10" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE10">
+      <c r="IN10" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO10">
+        <v>1</v>
+      </c>
+      <c r="IP10" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ10">
+        <v>1</v>
+      </c>
+      <c r="IR10" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS10" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT10" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU10" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV10" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW10">
         <v>86400</v>
       </c>
-      <c r="IF10">
+      <c r="IX10">
         <v>86400</v>
       </c>
-      <c r="IG10">
+      <c r="IY10">
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:241">
+    <row r="11" spans="1:259">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -7511,7 +8384,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7523,13 +8396,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>3125000</v>
+        <v>2532000</v>
       </c>
       <c r="O11" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="P11" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -7544,10 +8417,10 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="V11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="W11">
         <v>3</v>
@@ -7559,7 +8432,7 @@
         <v>20</v>
       </c>
       <c r="Z11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AA11">
         <v>3</v>
@@ -7571,13 +8444,13 @@
         <v>20</v>
       </c>
       <c r="AD11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AE11">
         <v>3</v>
       </c>
       <c r="AF11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AG11">
         <v>3</v>
@@ -7592,7 +8465,7 @@
         <v>6</v>
       </c>
       <c r="AM11" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -7607,10 +8480,10 @@
         <v>9</v>
       </c>
       <c r="AR11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="AS11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AT11">
         <v>3</v>
@@ -7622,7 +8495,7 @@
         <v>20</v>
       </c>
       <c r="AW11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AX11">
         <v>3</v>
@@ -7634,25 +8507,34 @@
         <v>20</v>
       </c>
       <c r="BA11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BB11">
         <v>3</v>
       </c>
       <c r="BC11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="BD11">
         <v>3</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BG11">
+        <v>5500000</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>288</v>
+      </c>
+      <c r="BI11">
+        <v>55</v>
       </c>
       <c r="BJ11" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="BK11">
         <v>1</v>
@@ -7667,10 +8549,10 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="BP11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BQ11">
         <v>3</v>
@@ -7682,7 +8564,7 @@
         <v>20</v>
       </c>
       <c r="BT11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BU11">
         <v>3</v>
@@ -7694,13 +8576,13 @@
         <v>20</v>
       </c>
       <c r="BX11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="BY11">
         <v>3</v>
       </c>
       <c r="BZ11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CA11">
         <v>0</v>
@@ -7709,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="CF11" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="CG11">
         <v>1</v>
@@ -7724,10 +8606,10 @@
         <v>9</v>
       </c>
       <c r="CK11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="CL11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CM11">
         <v>3</v>
@@ -7739,7 +8621,7 @@
         <v>20</v>
       </c>
       <c r="CP11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CQ11">
         <v>3</v>
@@ -7751,13 +8633,13 @@
         <v>20</v>
       </c>
       <c r="CT11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="CU11">
         <v>3</v>
       </c>
       <c r="CV11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="CW11">
         <v>3</v>
@@ -7769,10 +8651,10 @@
         <v>1</v>
       </c>
       <c r="CZ11">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="DA11" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="DB11">
         <v>0</v>
@@ -7784,7 +8666,7 @@
         <v>1</v>
       </c>
       <c r="DE11" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="DF11">
         <v>1</v>
@@ -7799,10 +8681,10 @@
         <v>9</v>
       </c>
       <c r="DJ11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="DK11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DL11">
         <v>3</v>
@@ -7814,7 +8696,7 @@
         <v>20</v>
       </c>
       <c r="DO11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DP11">
         <v>3</v>
@@ -7826,19 +8708,19 @@
         <v>20</v>
       </c>
       <c r="DS11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="DT11">
         <v>3</v>
       </c>
       <c r="DU11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="DV11">
         <v>3</v>
       </c>
       <c r="DW11" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="DX11">
         <v>0</v>
@@ -7847,7 +8729,7 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="ED11">
         <v>1</v>
@@ -7862,10 +8744,10 @@
         <v>9</v>
       </c>
       <c r="EH11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="EI11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EJ11">
         <v>3</v>
@@ -7877,7 +8759,7 @@
         <v>20</v>
       </c>
       <c r="EM11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="EN11">
         <v>3</v>
@@ -7889,19 +8771,19 @@
         <v>20</v>
       </c>
       <c r="EQ11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="ER11">
         <v>3</v>
       </c>
       <c r="ES11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="ET11">
         <v>3</v>
       </c>
       <c r="EU11" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="EV11">
         <v>0</v>
@@ -7910,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="FA11" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="FB11">
         <v>1</v>
@@ -7925,10 +8807,10 @@
         <v>9</v>
       </c>
       <c r="FF11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="FG11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FH11">
         <v>3</v>
@@ -7940,7 +8822,7 @@
         <v>20</v>
       </c>
       <c r="FK11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FL11">
         <v>3</v>
@@ -7952,144 +8834,216 @@
         <v>20</v>
       </c>
       <c r="FO11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="FP11">
         <v>3</v>
       </c>
       <c r="FQ11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="FR11">
         <v>3</v>
       </c>
       <c r="FS11" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="FT11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FU11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV11">
+        <v>2800</v>
+      </c>
+      <c r="FW11" t="s">
+        <v>295</v>
       </c>
       <c r="FX11" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="FY11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FZ11">
-        <v>0</v>
-      </c>
-      <c r="GS11" t="s">
-        <v>273</v>
-      </c>
-      <c r="GT11">
+        <v>1</v>
+      </c>
+      <c r="GA11">
+        <v>2</v>
+      </c>
+      <c r="GB11">
+        <v>9</v>
+      </c>
+      <c r="GC11" t="s">
+        <v>276</v>
+      </c>
+      <c r="GD11" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE11">
+        <v>3</v>
+      </c>
+      <c r="GF11">
+        <v>20</v>
+      </c>
+      <c r="GG11">
+        <v>20</v>
+      </c>
+      <c r="GH11" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI11">
+        <v>3</v>
+      </c>
+      <c r="GJ11">
+        <v>20</v>
+      </c>
+      <c r="GK11">
+        <v>20</v>
+      </c>
+      <c r="GL11" t="s">
+        <v>277</v>
+      </c>
+      <c r="GM11">
+        <v>3</v>
+      </c>
+      <c r="GN11" t="s">
+        <v>278</v>
+      </c>
+      <c r="GO11">
+        <v>3</v>
+      </c>
+      <c r="GP11" t="s">
+        <v>294</v>
+      </c>
+      <c r="GQ11">
+        <v>0</v>
+      </c>
+      <c r="GR11">
+        <v>0</v>
+      </c>
+      <c r="HK11" t="s">
+        <v>303</v>
+      </c>
+      <c r="HL11">
         <v>0.05</v>
       </c>
-      <c r="GU11">
+      <c r="HM11">
         <v>0.5</v>
       </c>
-      <c r="GV11">
+      <c r="HN11">
         <v>0.8</v>
       </c>
-      <c r="GW11">
+      <c r="HO11">
         <v>8.5</v>
       </c>
-      <c r="GX11" t="s">
-        <v>274</v>
-      </c>
-      <c r="GY11" t="s">
-        <v>275</v>
-      </c>
-      <c r="GZ11" t="s">
-        <v>267</v>
-      </c>
-      <c r="HA11">
-        <v>1</v>
-      </c>
-      <c r="HB11">
-        <v>1</v>
-      </c>
-      <c r="HC11">
-        <v>3100</v>
-      </c>
-      <c r="HD11">
-        <v>3100</v>
-      </c>
-      <c r="HE11">
+      <c r="HP11" t="s">
+        <v>304</v>
+      </c>
+      <c r="HQ11" t="s">
+        <v>305</v>
+      </c>
+      <c r="HR11" t="s">
+        <v>294</v>
+      </c>
+      <c r="HS11">
+        <v>1</v>
+      </c>
+      <c r="HT11">
+        <v>1</v>
+      </c>
+      <c r="HU11">
+        <v>2500</v>
+      </c>
+      <c r="HV11">
+        <v>2500</v>
+      </c>
+      <c r="HW11">
         <v>0.95</v>
       </c>
-      <c r="HF11">
+      <c r="HX11">
         <v>0.1</v>
       </c>
-      <c r="HG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH11" t="b">
-        <v>0</v>
-      </c>
-      <c r="HI11" t="s">
-        <v>267</v>
-      </c>
-      <c r="HJ11">
-        <v>0</v>
-      </c>
-      <c r="HK11">
-        <v>0</v>
-      </c>
-      <c r="HP11" t="s">
-        <v>267</v>
-      </c>
-      <c r="HQ11" t="s">
-        <v>276</v>
-      </c>
-      <c r="HR11" t="s">
-        <v>276</v>
-      </c>
-      <c r="HS11">
+      <c r="HY11" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="IA11" t="s">
+        <v>294</v>
+      </c>
+      <c r="IB11">
+        <v>1</v>
+      </c>
+      <c r="IC11">
+        <v>1</v>
+      </c>
+      <c r="ID11">
+        <v>2800</v>
+      </c>
+      <c r="IE11">
+        <v>5500</v>
+      </c>
+      <c r="IF11">
+        <v>0.95</v>
+      </c>
+      <c r="IG11">
+        <v>0.5</v>
+      </c>
+      <c r="IH11" t="s">
+        <v>294</v>
+      </c>
+      <c r="II11" t="s">
+        <v>306</v>
+      </c>
+      <c r="IJ11" t="s">
+        <v>306</v>
+      </c>
+      <c r="IK11">
         <v>86400</v>
       </c>
-      <c r="HT11" t="s">
-        <v>277</v>
-      </c>
-      <c r="HU11">
+      <c r="IL11" t="s">
+        <v>307</v>
+      </c>
+      <c r="IM11">
         <v>86400</v>
       </c>
-      <c r="HV11" t="s">
-        <v>262</v>
-      </c>
-      <c r="HW11">
-        <v>1</v>
-      </c>
-      <c r="HX11" t="s">
-        <v>262</v>
-      </c>
-      <c r="HY11">
-        <v>1</v>
-      </c>
-      <c r="HZ11" t="s">
-        <v>278</v>
-      </c>
-      <c r="IA11" t="s">
-        <v>262</v>
-      </c>
-      <c r="IB11" t="s">
-        <v>262</v>
-      </c>
-      <c r="IC11" t="s">
-        <v>262</v>
-      </c>
-      <c r="ID11" t="s">
-        <v>278</v>
-      </c>
-      <c r="IE11">
+      <c r="IN11" t="s">
+        <v>289</v>
+      </c>
+      <c r="IO11">
+        <v>1</v>
+      </c>
+      <c r="IP11" t="s">
+        <v>289</v>
+      </c>
+      <c r="IQ11">
+        <v>1</v>
+      </c>
+      <c r="IR11" t="s">
+        <v>308</v>
+      </c>
+      <c r="IS11" t="s">
+        <v>289</v>
+      </c>
+      <c r="IT11" t="s">
+        <v>289</v>
+      </c>
+      <c r="IU11" t="s">
+        <v>289</v>
+      </c>
+      <c r="IV11" t="s">
+        <v>308</v>
+      </c>
+      <c r="IW11">
         <v>86400</v>
       </c>
-      <c r="IF11">
+      <c r="IX11">
         <v>86400</v>
       </c>
-      <c r="IG11">
+      <c r="IY11">
         <v>3600</v>
       </c>
     </row>
@@ -8117,13 +9071,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -8345,7 +9299,7 @@
         <v>76</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="CE1" s="1" t="s">
         <v>77</v>
@@ -8651,184 +9605,184 @@
         <v>177</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="HM1" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="HN1" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="HO1" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="HP1" s="1" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="HQ1" s="1" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="HR1" s="1" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="IC1" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="ID1" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="IE1" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="IF1" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="IG1" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="IH1" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="II1" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -8855,7 +9809,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -9221,133 +10175,133 @@
         <v>173</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -9374,7 +10328,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -9740,160 +10694,160 @@
         <v>173</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -10145,76 +11099,76 @@
         <v>173</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -10244,130 +11198,130 @@
         <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/02_config/example_single_market/agents.xlsx
+++ b/02_config/example_single_market/agents.xlsx
@@ -8,18 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="sfh" sheetId="1" r:id="rId1"/>
-    <sheet name="mfh" sheetId="2" r:id="rId2"/>
-    <sheet name="ctsp" sheetId="3" r:id="rId3"/>
-    <sheet name="industry" sheetId="4" r:id="rId4"/>
-    <sheet name="producer" sheetId="5" r:id="rId5"/>
-    <sheet name="storage" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="310">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -759,6 +754,12 @@
     <t>ems/market/horizon</t>
   </si>
   <si>
+    <t>ems/market/linear/steps_to_final</t>
+  </si>
+  <si>
+    <t>ems/market/linear/steps_from_init</t>
+  </si>
+  <si>
     <t>ems/market/fcast/local/method</t>
   </si>
   <si>
@@ -795,57 +796,57 @@
     <t>ems/fcasts/update</t>
   </si>
   <si>
-    <t>o8RENvmIJHHNd1l</t>
-  </si>
-  <si>
-    <t>I90EqWRtDwkBV26</t>
-  </si>
-  <si>
-    <t>A0hRymeCrOZSb8w</t>
-  </si>
-  <si>
-    <t>FOSMD7SSeMwEjUC</t>
-  </si>
-  <si>
-    <t>67aIDazktWn6yzC</t>
-  </si>
-  <si>
-    <t>vMMDGls8ojIM2vT</t>
-  </si>
-  <si>
-    <t>ypY3kBiRXLP0Gfn</t>
-  </si>
-  <si>
-    <t>HqZsrPIjCXt8ECE</t>
-  </si>
-  <si>
-    <t>dEY0eRjw9O27gIv</t>
-  </si>
-  <si>
-    <t>SekGK0Bo2wtyeck</t>
+    <t>ifN99SiKLbKqLYQ</t>
+  </si>
+  <si>
+    <t>1rFqHq2yJJfxOl6</t>
+  </si>
+  <si>
+    <t>hslCyhEIwteqbFy</t>
+  </si>
+  <si>
+    <t>xjT3hE41RNaKDoD</t>
+  </si>
+  <si>
+    <t>nAaQFs09neeF8xj</t>
+  </si>
+  <si>
+    <t>S7HAdQZw0nf7sqC</t>
+  </si>
+  <si>
+    <t>s5HnQLfyUPkWATP</t>
+  </si>
+  <si>
+    <t>FGKCErYnity7r96</t>
+  </si>
+  <si>
+    <t>2JnALEtKzJcp7HZ</t>
+  </si>
+  <si>
+    <t>hFAQQgIRFgN33KY</t>
+  </si>
+  <si>
+    <t>hh_2455_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4402_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2896_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
   </si>
   <si>
     <t>hh_4536_0.csv</t>
   </si>
   <si>
-    <t>hh_2896_0.csv</t>
-  </si>
-  <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_4402_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2532_0.csv</t>
-  </si>
-  <si>
     <t>perfect</t>
   </si>
   <si>
@@ -861,31 +862,28 @@
     <t>rfr</t>
   </si>
   <si>
-    <t>heat_4536_0.csv</t>
+    <t>heat_2455_0.csv</t>
+  </si>
+  <si>
+    <t>heat_4402_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3863_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
   </si>
   <si>
     <t>heat_2896_0.csv</t>
   </si>
   <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
     <t>heat_5527_0.csv</t>
   </si>
   <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_3125_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_4402_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_5_pu.csv</t>
+    <t>heat_gen_0_pu.csv</t>
   </si>
   <si>
     <t>naive</t>
@@ -897,37 +895,37 @@
     <t>pv_config.json</t>
   </si>
   <si>
+    <t>green_local</t>
+  </si>
+  <si>
     <t>weather</t>
   </si>
   <si>
-    <t>green_local</t>
-  </si>
-  <si>
     <t>local</t>
   </si>
   <si>
+    <t>hp_DAIKIN Europe_ground.json</t>
+  </si>
+  <si>
     <t>hp_Bosch Thermotechnik_air.json</t>
   </si>
   <si>
-    <t>hp_DAIKIN Europe_ground.json</t>
+    <t>ev_fulltime_41.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_46.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_2.csv</t>
   </si>
   <si>
     <t>ev_freetime_1.csv</t>
   </si>
   <si>
-    <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_48.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_46.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_89.csv</t>
+    <t>ev_fulltime_43.csv</t>
   </si>
   <si>
     <t>min_soc</t>
@@ -946,96 +944,6 @@
   </si>
   <si>
     <t>['naive', 'naive']</t>
-  </si>
-  <si>
-    <t>general/sub_id</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments_independent</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments</t>
-  </si>
-  <si>
-    <t>heat/fcast/arima/days</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/local</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/wholesale</t>
-  </si>
-  <si>
-    <t>general/parameters/type</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/price_sensitive_threshold</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_val</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_time_val</t>
-  </si>
-  <si>
-    <t>ev/charging_scheme/min_soc_time_time</t>
-  </si>
-  <si>
-    <t>ev/fcast/random_forest_classifier/features</t>
-  </si>
-  <si>
-    <t>psh/owner</t>
-  </si>
-  <si>
-    <t>psh/num</t>
-  </si>
-  <si>
-    <t>psh/sizing/power_0</t>
-  </si>
-  <si>
-    <t>psh/sizing/capacity_0</t>
-  </si>
-  <si>
-    <t>psh/sizing/efficiency_0</t>
-  </si>
-  <si>
-    <t>psh/sizing/soc_0</t>
-  </si>
-  <si>
-    <t>psh/sizing/g2psh_0</t>
-  </si>
-  <si>
-    <t>psh/sizing/psh2g_0</t>
-  </si>
-  <si>
-    <t>psh/quality</t>
-  </si>
-  <si>
-    <t>hydrogen/owner</t>
-  </si>
-  <si>
-    <t>hydrogen/num</t>
-  </si>
-  <si>
-    <t>hydrogen/sizing/power_0</t>
-  </si>
-  <si>
-    <t>hydrogen/sizing/capacity_0</t>
-  </si>
-  <si>
-    <t>hydrogen/sizing/efficiency_0</t>
-  </si>
-  <si>
-    <t>hydrogen/sizing/soc_0</t>
-  </si>
-  <si>
-    <t>hydrogen/sizing/g2h2_0</t>
-  </si>
-  <si>
-    <t>hydrogen/sizing/h22g_0</t>
-  </si>
-  <si>
-    <t>hydrogen/quality</t>
   </si>
 </sst>
 </file>
@@ -1393,10 +1301,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:IY11"/>
+  <dimension ref="A1:JA11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:259">
+    <row r="1" spans="1:261">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2171,19 +2079,25 @@
       <c r="IY1" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="IZ1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="JA1" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
-    <row r="2" spans="1:259">
+    <row r="2" spans="1:261">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -2192,7 +2106,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -2204,13 +2118,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>4536000</v>
+        <v>2455000</v>
       </c>
       <c r="O2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2225,10 +2139,10 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W2">
         <v>3</v>
@@ -2240,7 +2154,7 @@
         <v>20</v>
       </c>
       <c r="Z2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA2">
         <v>3</v>
@@ -2252,13 +2166,13 @@
         <v>20</v>
       </c>
       <c r="AD2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE2">
         <v>3</v>
       </c>
       <c r="AF2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG2">
         <v>3</v>
@@ -2273,7 +2187,7 @@
         <v>6</v>
       </c>
       <c r="AM2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -2288,10 +2202,10 @@
         <v>9</v>
       </c>
       <c r="AR2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT2">
         <v>3</v>
@@ -2303,7 +2217,7 @@
         <v>20</v>
       </c>
       <c r="AW2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX2">
         <v>3</v>
@@ -2315,13 +2229,13 @@
         <v>20</v>
       </c>
       <c r="BA2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB2">
         <v>3</v>
       </c>
       <c r="BC2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD2">
         <v>3</v>
@@ -2333,16 +2247,16 @@
         <v>1</v>
       </c>
       <c r="BG2">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BH2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="BI2">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BJ2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK2">
         <v>1</v>
@@ -2357,10 +2271,10 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ2">
         <v>3</v>
@@ -2372,7 +2286,7 @@
         <v>20</v>
       </c>
       <c r="BT2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU2">
         <v>3</v>
@@ -2384,13 +2298,13 @@
         <v>20</v>
       </c>
       <c r="BX2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY2">
         <v>3</v>
       </c>
       <c r="BZ2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -2399,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="CF2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG2">
         <v>1</v>
@@ -2414,10 +2328,10 @@
         <v>9</v>
       </c>
       <c r="CK2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM2">
         <v>3</v>
@@ -2429,7 +2343,7 @@
         <v>20</v>
       </c>
       <c r="CP2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ2">
         <v>3</v>
@@ -2441,25 +2355,40 @@
         <v>20</v>
       </c>
       <c r="CT2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU2">
         <v>3</v>
       </c>
       <c r="CV2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW2">
         <v>3</v>
       </c>
       <c r="CX2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CZ2">
+        <v>3400</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>292</v>
+      </c>
+      <c r="DB2">
+        <v>-20</v>
+      </c>
+      <c r="DC2">
+        <v>50</v>
+      </c>
+      <c r="DD2" t="b">
+        <v>1</v>
       </c>
       <c r="DE2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF2">
         <v>1</v>
@@ -2474,10 +2403,10 @@
         <v>9</v>
       </c>
       <c r="DJ2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL2">
         <v>3</v>
@@ -2489,7 +2418,7 @@
         <v>20</v>
       </c>
       <c r="DO2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP2">
         <v>3</v>
@@ -2501,13 +2430,13 @@
         <v>20</v>
       </c>
       <c r="DS2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT2">
         <v>3</v>
       </c>
       <c r="DU2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV2">
         <v>3</v>
@@ -2522,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -2537,10 +2466,10 @@
         <v>9</v>
       </c>
       <c r="EH2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ2">
         <v>3</v>
@@ -2552,7 +2481,7 @@
         <v>20</v>
       </c>
       <c r="EM2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN2">
         <v>3</v>
@@ -2564,13 +2493,13 @@
         <v>20</v>
       </c>
       <c r="EQ2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER2">
         <v>3</v>
       </c>
       <c r="ES2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET2">
         <v>3</v>
@@ -2585,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="FA2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB2">
         <v>1</v>
@@ -2600,10 +2529,10 @@
         <v>9</v>
       </c>
       <c r="FF2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH2">
         <v>3</v>
@@ -2615,7 +2544,7 @@
         <v>20</v>
       </c>
       <c r="FK2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL2">
         <v>3</v>
@@ -2627,19 +2556,19 @@
         <v>20</v>
       </c>
       <c r="FO2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP2">
         <v>3</v>
       </c>
       <c r="FQ2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR2">
         <v>3</v>
       </c>
       <c r="FS2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT2">
         <v>1</v>
@@ -2648,13 +2577,13 @@
         <v>1</v>
       </c>
       <c r="FV2">
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="FW2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="FX2" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY2">
         <v>1</v>
@@ -2669,10 +2598,10 @@
         <v>9</v>
       </c>
       <c r="GC2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE2">
         <v>3</v>
@@ -2684,7 +2613,7 @@
         <v>20</v>
       </c>
       <c r="GH2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI2">
         <v>3</v>
@@ -2696,88 +2625,34 @@
         <v>20</v>
       </c>
       <c r="GL2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM2">
         <v>3</v>
       </c>
       <c r="GN2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO2">
         <v>3</v>
       </c>
       <c r="GP2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="GR2">
-        <v>2</v>
-      </c>
-      <c r="GS2" t="s">
-        <v>297</v>
-      </c>
-      <c r="GT2">
-        <v>75000</v>
-      </c>
-      <c r="GU2">
-        <v>7200</v>
-      </c>
-      <c r="GV2">
-        <v>11000</v>
-      </c>
-      <c r="GW2">
-        <v>100000</v>
-      </c>
-      <c r="GX2">
-        <v>0.9</v>
-      </c>
-      <c r="GY2">
-        <v>0.8</v>
-      </c>
-      <c r="GZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="HA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="HB2" t="s">
-        <v>302</v>
-      </c>
-      <c r="HC2">
-        <v>100000</v>
-      </c>
-      <c r="HD2">
-        <v>11000</v>
-      </c>
-      <c r="HE2">
-        <v>22000</v>
-      </c>
-      <c r="HF2">
-        <v>200000</v>
-      </c>
-      <c r="HG2">
-        <v>0.9</v>
-      </c>
-      <c r="HH2">
-        <v>0.8</v>
-      </c>
-      <c r="HI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="HJ2" t="b">
         <v>0</v>
       </c>
       <c r="HK2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL2">
         <v>0.05</v>
       </c>
       <c r="HM2">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN2">
         <v>0.8</v>
@@ -2786,22 +2661,40 @@
         <v>8.5</v>
       </c>
       <c r="HP2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="HT2">
+        <v>1</v>
+      </c>
+      <c r="HU2">
+        <v>2500</v>
+      </c>
+      <c r="HV2">
+        <v>2500</v>
+      </c>
+      <c r="HW2">
+        <v>0.95</v>
+      </c>
+      <c r="HX2">
+        <v>0.1</v>
+      </c>
+      <c r="HY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ2" t="b">
         <v>0</v>
       </c>
       <c r="IA2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB2">
         <v>1</v>
@@ -2810,10 +2703,10 @@
         <v>1</v>
       </c>
       <c r="ID2">
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="IE2">
-        <v>19500</v>
+        <v>5500</v>
       </c>
       <c r="IF2">
         <v>0.95</v>
@@ -2822,66 +2715,72 @@
         <v>0.5</v>
       </c>
       <c r="IH2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK2">
         <v>86400</v>
       </c>
       <c r="IL2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM2">
+        <v>57600</v>
+      </c>
+      <c r="IN2">
+        <v>1</v>
+      </c>
+      <c r="IO2">
+        <v>0</v>
+      </c>
+      <c r="IP2" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ2">
+        <v>1</v>
+      </c>
+      <c r="IR2" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS2">
+        <v>1</v>
+      </c>
+      <c r="IT2" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU2" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV2" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW2" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX2" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY2">
         <v>86400</v>
       </c>
-      <c r="IN2" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO2">
-        <v>1</v>
-      </c>
-      <c r="IP2" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ2">
-        <v>1</v>
-      </c>
-      <c r="IR2" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS2" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT2" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU2" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV2" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW2">
+      <c r="IZ2">
         <v>86400</v>
       </c>
-      <c r="IX2">
-        <v>86400</v>
-      </c>
-      <c r="IY2">
+      <c r="JA2">
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:259">
+    <row r="3" spans="1:261">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -2908,13 +2807,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>2896000</v>
+        <v>4402000</v>
       </c>
       <c r="O3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2929,10 +2828,10 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -2944,7 +2843,7 @@
         <v>20</v>
       </c>
       <c r="Z3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA3">
         <v>3</v>
@@ -2956,13 +2855,13 @@
         <v>20</v>
       </c>
       <c r="AD3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE3">
         <v>3</v>
       </c>
       <c r="AF3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG3">
         <v>3</v>
@@ -2977,7 +2876,7 @@
         <v>6</v>
       </c>
       <c r="AM3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -2992,10 +2891,10 @@
         <v>9</v>
       </c>
       <c r="AR3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT3">
         <v>3</v>
@@ -3007,7 +2906,7 @@
         <v>20</v>
       </c>
       <c r="AW3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX3">
         <v>3</v>
@@ -3019,13 +2918,13 @@
         <v>20</v>
       </c>
       <c r="BA3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB3">
         <v>3</v>
       </c>
       <c r="BC3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD3">
         <v>3</v>
@@ -3040,13 +2939,13 @@
         <v>19500000</v>
       </c>
       <c r="BH3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="BI3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BJ3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK3">
         <v>1</v>
@@ -3061,10 +2960,10 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ3">
         <v>3</v>
@@ -3076,7 +2975,7 @@
         <v>20</v>
       </c>
       <c r="BT3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU3">
         <v>3</v>
@@ -3088,13 +2987,13 @@
         <v>20</v>
       </c>
       <c r="BX3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY3">
         <v>3</v>
       </c>
       <c r="BZ3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA3">
         <v>0</v>
@@ -3103,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="CF3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG3">
         <v>1</v>
@@ -3118,10 +3017,10 @@
         <v>9</v>
       </c>
       <c r="CK3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM3">
         <v>3</v>
@@ -3133,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="CP3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ3">
         <v>3</v>
@@ -3145,25 +3044,40 @@
         <v>20</v>
       </c>
       <c r="CT3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU3">
         <v>3</v>
       </c>
       <c r="CV3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW3">
         <v>3</v>
       </c>
       <c r="CX3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CZ3">
+        <v>7900</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>292</v>
+      </c>
+      <c r="DB3">
+        <v>0</v>
+      </c>
+      <c r="DC3">
+        <v>40</v>
+      </c>
+      <c r="DD3" t="b">
+        <v>1</v>
       </c>
       <c r="DE3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF3">
         <v>1</v>
@@ -3178,10 +3092,10 @@
         <v>9</v>
       </c>
       <c r="DJ3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL3">
         <v>3</v>
@@ -3193,7 +3107,7 @@
         <v>20</v>
       </c>
       <c r="DO3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP3">
         <v>3</v>
@@ -3205,13 +3119,13 @@
         <v>20</v>
       </c>
       <c r="DS3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT3">
         <v>3</v>
       </c>
       <c r="DU3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV3">
         <v>3</v>
@@ -3226,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED3">
         <v>1</v>
@@ -3241,10 +3155,10 @@
         <v>9</v>
       </c>
       <c r="EH3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ3">
         <v>3</v>
@@ -3256,7 +3170,7 @@
         <v>20</v>
       </c>
       <c r="EM3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN3">
         <v>3</v>
@@ -3268,13 +3182,13 @@
         <v>20</v>
       </c>
       <c r="EQ3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER3">
         <v>3</v>
       </c>
       <c r="ES3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET3">
         <v>3</v>
@@ -3289,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="FA3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB3">
         <v>1</v>
@@ -3304,10 +3218,10 @@
         <v>9</v>
       </c>
       <c r="FF3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH3">
         <v>3</v>
@@ -3319,7 +3233,7 @@
         <v>20</v>
       </c>
       <c r="FK3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL3">
         <v>3</v>
@@ -3331,19 +3245,19 @@
         <v>20</v>
       </c>
       <c r="FO3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP3">
         <v>3</v>
       </c>
       <c r="FQ3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR3">
         <v>3</v>
       </c>
       <c r="FS3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT3">
         <v>1</v>
@@ -3355,10 +3269,10 @@
         <v>9800</v>
       </c>
       <c r="FW3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="FX3" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY3">
         <v>1</v>
@@ -3373,10 +3287,10 @@
         <v>9</v>
       </c>
       <c r="GC3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE3">
         <v>3</v>
@@ -3388,7 +3302,7 @@
         <v>20</v>
       </c>
       <c r="GH3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI3">
         <v>3</v>
@@ -3400,61 +3314,34 @@
         <v>20</v>
       </c>
       <c r="GL3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM3">
         <v>3</v>
       </c>
       <c r="GN3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO3">
         <v>3</v>
       </c>
       <c r="GP3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="GR3">
-        <v>1</v>
-      </c>
-      <c r="GS3" t="s">
-        <v>298</v>
-      </c>
-      <c r="GT3">
-        <v>75000</v>
-      </c>
-      <c r="GU3">
-        <v>7200</v>
-      </c>
-      <c r="GV3">
-        <v>11000</v>
-      </c>
-      <c r="GW3">
-        <v>100000</v>
-      </c>
-      <c r="GX3">
-        <v>0.9</v>
-      </c>
-      <c r="GY3">
-        <v>0.8</v>
-      </c>
-      <c r="GZ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="HA3" t="b">
         <v>0</v>
       </c>
       <c r="HK3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL3">
         <v>0.05</v>
       </c>
       <c r="HM3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN3">
         <v>0.8</v>
@@ -3463,22 +3350,40 @@
         <v>8.5</v>
       </c>
       <c r="HP3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="HT3">
+        <v>1</v>
+      </c>
+      <c r="HU3">
+        <v>4400</v>
+      </c>
+      <c r="HV3">
+        <v>4400</v>
+      </c>
+      <c r="HW3">
+        <v>0.95</v>
+      </c>
+      <c r="HX3">
+        <v>0.1</v>
+      </c>
+      <c r="HY3" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ3" t="b">
         <v>0</v>
       </c>
       <c r="IA3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB3">
         <v>1</v>
@@ -3499,72 +3404,78 @@
         <v>0.5</v>
       </c>
       <c r="IH3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK3">
         <v>86400</v>
       </c>
       <c r="IL3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM3">
+        <v>57600</v>
+      </c>
+      <c r="IN3">
+        <v>1</v>
+      </c>
+      <c r="IO3">
+        <v>0</v>
+      </c>
+      <c r="IP3" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ3">
+        <v>1</v>
+      </c>
+      <c r="IR3" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS3">
+        <v>1</v>
+      </c>
+      <c r="IT3" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU3" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV3" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW3" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX3" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY3">
         <v>86400</v>
       </c>
-      <c r="IN3" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO3">
-        <v>1</v>
-      </c>
-      <c r="IP3" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ3">
-        <v>1</v>
-      </c>
-      <c r="IR3" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS3" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT3" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU3" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV3" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW3">
+      <c r="IZ3">
         <v>86400</v>
       </c>
-      <c r="IX3">
-        <v>86400</v>
-      </c>
-      <c r="IY3">
+      <c r="JA3">
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:259">
+    <row r="4" spans="1:261">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -3573,7 +3484,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -3585,13 +3496,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>5527000</v>
+        <v>3863000</v>
       </c>
       <c r="O4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3606,10 +3517,10 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -3621,7 +3532,7 @@
         <v>20</v>
       </c>
       <c r="Z4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA4">
         <v>3</v>
@@ -3633,13 +3544,13 @@
         <v>20</v>
       </c>
       <c r="AD4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE4">
         <v>3</v>
       </c>
       <c r="AF4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG4">
         <v>3</v>
@@ -3654,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="AM4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -3669,10 +3580,10 @@
         <v>9</v>
       </c>
       <c r="AR4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT4">
         <v>3</v>
@@ -3684,7 +3595,7 @@
         <v>20</v>
       </c>
       <c r="AW4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX4">
         <v>3</v>
@@ -3696,13 +3607,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB4">
         <v>3</v>
       </c>
       <c r="BC4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD4">
         <v>3</v>
@@ -3714,16 +3625,16 @@
         <v>1</v>
       </c>
       <c r="BG4">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BH4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="BI4">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BJ4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK4">
         <v>1</v>
@@ -3738,10 +3649,10 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ4">
         <v>3</v>
@@ -3753,7 +3664,7 @@
         <v>20</v>
       </c>
       <c r="BT4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU4">
         <v>3</v>
@@ -3765,13 +3676,13 @@
         <v>20</v>
       </c>
       <c r="BX4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY4">
         <v>3</v>
       </c>
       <c r="BZ4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA4">
         <v>0</v>
@@ -3780,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="CF4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG4">
         <v>1</v>
@@ -3795,10 +3706,10 @@
         <v>9</v>
       </c>
       <c r="CK4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM4">
         <v>3</v>
@@ -3810,7 +3721,7 @@
         <v>20</v>
       </c>
       <c r="CP4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ4">
         <v>3</v>
@@ -3822,13 +3733,13 @@
         <v>20</v>
       </c>
       <c r="CT4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU4">
         <v>3</v>
       </c>
       <c r="CV4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW4">
         <v>3</v>
@@ -3840,10 +3751,10 @@
         <v>1</v>
       </c>
       <c r="CZ4">
-        <v>8600</v>
+        <v>6500</v>
       </c>
       <c r="DA4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DB4">
         <v>0</v>
@@ -3855,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="DE4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF4">
         <v>1</v>
@@ -3870,10 +3781,10 @@
         <v>9</v>
       </c>
       <c r="DJ4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL4">
         <v>3</v>
@@ -3885,7 +3796,7 @@
         <v>20</v>
       </c>
       <c r="DO4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP4">
         <v>3</v>
@@ -3897,13 +3808,13 @@
         <v>20</v>
       </c>
       <c r="DS4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT4">
         <v>3</v>
       </c>
       <c r="DU4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV4">
         <v>3</v>
@@ -3918,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED4">
         <v>1</v>
@@ -3933,10 +3844,10 @@
         <v>9</v>
       </c>
       <c r="EH4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ4">
         <v>3</v>
@@ -3948,7 +3859,7 @@
         <v>20</v>
       </c>
       <c r="EM4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN4">
         <v>3</v>
@@ -3960,13 +3871,13 @@
         <v>20</v>
       </c>
       <c r="EQ4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER4">
         <v>3</v>
       </c>
       <c r="ES4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET4">
         <v>3</v>
@@ -3981,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="FA4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB4">
         <v>1</v>
@@ -3996,10 +3907,10 @@
         <v>9</v>
       </c>
       <c r="FF4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH4">
         <v>3</v>
@@ -4011,7 +3922,7 @@
         <v>20</v>
       </c>
       <c r="FK4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL4">
         <v>3</v>
@@ -4023,19 +3934,19 @@
         <v>20</v>
       </c>
       <c r="FO4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP4">
         <v>3</v>
       </c>
       <c r="FQ4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR4">
         <v>3</v>
       </c>
       <c r="FS4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT4">
         <v>1</v>
@@ -4044,13 +3955,13 @@
         <v>1</v>
       </c>
       <c r="FV4">
-        <v>2800</v>
+        <v>9800</v>
       </c>
       <c r="FW4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="FX4" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY4">
         <v>1</v>
@@ -4065,10 +3976,10 @@
         <v>9</v>
       </c>
       <c r="GC4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE4">
         <v>3</v>
@@ -4080,7 +3991,7 @@
         <v>20</v>
       </c>
       <c r="GH4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI4">
         <v>3</v>
@@ -4092,19 +4003,19 @@
         <v>20</v>
       </c>
       <c r="GL4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM4">
         <v>3</v>
       </c>
       <c r="GN4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO4">
         <v>3</v>
       </c>
       <c r="GP4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ4">
         <v>0</v>
@@ -4113,13 +4024,13 @@
         <v>0</v>
       </c>
       <c r="HK4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL4">
         <v>0.05</v>
       </c>
       <c r="HM4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN4">
         <v>0.8</v>
@@ -4128,22 +4039,40 @@
         <v>8.5</v>
       </c>
       <c r="HP4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="HT4">
+        <v>1</v>
+      </c>
+      <c r="HU4">
+        <v>3900</v>
+      </c>
+      <c r="HV4">
+        <v>3900</v>
+      </c>
+      <c r="HW4">
+        <v>0.95</v>
+      </c>
+      <c r="HX4">
+        <v>0.1</v>
+      </c>
+      <c r="HY4" t="b">
+        <v>0</v>
+      </c>
+      <c r="HZ4" t="b">
         <v>0</v>
       </c>
       <c r="IA4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB4">
         <v>1</v>
@@ -4152,10 +4081,10 @@
         <v>1</v>
       </c>
       <c r="ID4">
-        <v>2800</v>
+        <v>9800</v>
       </c>
       <c r="IE4">
-        <v>5500</v>
+        <v>19500</v>
       </c>
       <c r="IF4">
         <v>0.95</v>
@@ -4164,66 +4093,72 @@
         <v>0.5</v>
       </c>
       <c r="IH4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK4">
         <v>86400</v>
       </c>
       <c r="IL4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM4">
+        <v>72000</v>
+      </c>
+      <c r="IN4">
+        <v>1</v>
+      </c>
+      <c r="IO4">
+        <v>0</v>
+      </c>
+      <c r="IP4" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ4">
+        <v>1</v>
+      </c>
+      <c r="IR4" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS4">
+        <v>1</v>
+      </c>
+      <c r="IT4" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU4" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV4" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW4" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX4" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY4">
         <v>86400</v>
       </c>
-      <c r="IN4" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO4">
-        <v>1</v>
-      </c>
-      <c r="IP4" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ4">
-        <v>1</v>
-      </c>
-      <c r="IR4" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS4" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT4" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU4" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV4" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW4">
+      <c r="IZ4">
         <v>86400</v>
       </c>
-      <c r="IX4">
-        <v>86400</v>
-      </c>
-      <c r="IY4">
+      <c r="JA4">
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:259">
+    <row r="5" spans="1:261">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -4250,13 +4185,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>3648000</v>
+        <v>4402000</v>
       </c>
       <c r="O5" t="s">
         <v>271</v>
       </c>
       <c r="P5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -4271,10 +4206,10 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -4286,7 +4221,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA5">
         <v>3</v>
@@ -4298,13 +4233,13 @@
         <v>20</v>
       </c>
       <c r="AD5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE5">
         <v>3</v>
       </c>
       <c r="AF5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG5">
         <v>3</v>
@@ -4319,7 +4254,7 @@
         <v>6</v>
       </c>
       <c r="AM5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -4334,10 +4269,10 @@
         <v>9</v>
       </c>
       <c r="AR5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT5">
         <v>3</v>
@@ -4349,7 +4284,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX5">
         <v>3</v>
@@ -4361,13 +4296,13 @@
         <v>20</v>
       </c>
       <c r="BA5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB5">
         <v>3</v>
       </c>
       <c r="BC5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD5">
         <v>3</v>
@@ -4382,13 +4317,13 @@
         <v>19500000</v>
       </c>
       <c r="BH5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="BI5">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BJ5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK5">
         <v>1</v>
@@ -4403,10 +4338,10 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ5">
         <v>3</v>
@@ -4418,7 +4353,7 @@
         <v>20</v>
       </c>
       <c r="BT5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU5">
         <v>3</v>
@@ -4430,13 +4365,13 @@
         <v>20</v>
       </c>
       <c r="BX5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY5">
         <v>3</v>
       </c>
       <c r="BZ5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA5">
         <v>0</v>
@@ -4445,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="CF5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG5">
         <v>1</v>
@@ -4460,10 +4395,10 @@
         <v>9</v>
       </c>
       <c r="CK5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM5">
         <v>3</v>
@@ -4475,7 +4410,7 @@
         <v>20</v>
       </c>
       <c r="CP5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ5">
         <v>3</v>
@@ -4487,13 +4422,13 @@
         <v>20</v>
       </c>
       <c r="CT5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU5">
         <v>3</v>
       </c>
       <c r="CV5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW5">
         <v>3</v>
@@ -4505,22 +4440,22 @@
         <v>1</v>
       </c>
       <c r="CZ5">
-        <v>4900</v>
+        <v>5600</v>
       </c>
       <c r="DA5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DB5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="DC5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DD5" t="b">
         <v>1</v>
       </c>
       <c r="DE5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF5">
         <v>1</v>
@@ -4535,10 +4470,10 @@
         <v>9</v>
       </c>
       <c r="DJ5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL5">
         <v>3</v>
@@ -4550,7 +4485,7 @@
         <v>20</v>
       </c>
       <c r="DO5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP5">
         <v>3</v>
@@ -4562,13 +4497,13 @@
         <v>20</v>
       </c>
       <c r="DS5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT5">
         <v>3</v>
       </c>
       <c r="DU5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV5">
         <v>3</v>
@@ -4583,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED5">
         <v>1</v>
@@ -4598,10 +4533,10 @@
         <v>9</v>
       </c>
       <c r="EH5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ5">
         <v>3</v>
@@ -4613,7 +4548,7 @@
         <v>20</v>
       </c>
       <c r="EM5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN5">
         <v>3</v>
@@ -4625,13 +4560,13 @@
         <v>20</v>
       </c>
       <c r="EQ5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER5">
         <v>3</v>
       </c>
       <c r="ES5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET5">
         <v>3</v>
@@ -4646,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="FA5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB5">
         <v>1</v>
@@ -4661,10 +4596,10 @@
         <v>9</v>
       </c>
       <c r="FF5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH5">
         <v>3</v>
@@ -4676,7 +4611,7 @@
         <v>20</v>
       </c>
       <c r="FK5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL5">
         <v>3</v>
@@ -4688,19 +4623,19 @@
         <v>20</v>
       </c>
       <c r="FO5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP5">
         <v>3</v>
       </c>
       <c r="FQ5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR5">
         <v>3</v>
       </c>
       <c r="FS5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT5">
         <v>1</v>
@@ -4712,10 +4647,10 @@
         <v>9800</v>
       </c>
       <c r="FW5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="FX5" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY5">
         <v>1</v>
@@ -4730,10 +4665,10 @@
         <v>9</v>
       </c>
       <c r="GC5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE5">
         <v>3</v>
@@ -4745,7 +4680,7 @@
         <v>20</v>
       </c>
       <c r="GH5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI5">
         <v>3</v>
@@ -4757,40 +4692,40 @@
         <v>20</v>
       </c>
       <c r="GL5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM5">
         <v>3</v>
       </c>
       <c r="GN5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO5">
         <v>3</v>
       </c>
       <c r="GP5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ5">
         <v>1</v>
       </c>
       <c r="GR5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="GS5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="GT5">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="GU5">
         <v>7200</v>
       </c>
       <c r="GV5">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GW5">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="GX5">
         <v>0.9</v>
@@ -4804,14 +4739,41 @@
       <c r="HA5" t="b">
         <v>0</v>
       </c>
+      <c r="HB5" t="s">
+        <v>303</v>
+      </c>
+      <c r="HC5">
+        <v>50000</v>
+      </c>
+      <c r="HD5">
+        <v>7200</v>
+      </c>
+      <c r="HE5">
+        <v>7200</v>
+      </c>
+      <c r="HF5">
+        <v>50000</v>
+      </c>
+      <c r="HG5">
+        <v>0.9</v>
+      </c>
+      <c r="HH5">
+        <v>0.8</v>
+      </c>
+      <c r="HI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="HJ5" t="b">
+        <v>0</v>
+      </c>
       <c r="HK5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL5">
         <v>0.05</v>
       </c>
       <c r="HM5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN5">
         <v>0.8</v>
@@ -4820,13 +4782,13 @@
         <v>8.5</v>
       </c>
       <c r="HP5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS5">
         <v>1</v>
@@ -4835,10 +4797,10 @@
         <v>1</v>
       </c>
       <c r="HU5">
-        <v>3600</v>
+        <v>4400</v>
       </c>
       <c r="HV5">
-        <v>3600</v>
+        <v>4400</v>
       </c>
       <c r="HW5">
         <v>0.95</v>
@@ -4853,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="IA5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB5">
         <v>1</v>
@@ -4874,66 +4836,72 @@
         <v>0.5</v>
       </c>
       <c r="IH5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK5">
         <v>86400</v>
       </c>
       <c r="IL5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM5">
+        <v>57600</v>
+      </c>
+      <c r="IN5">
+        <v>1</v>
+      </c>
+      <c r="IO5">
+        <v>0</v>
+      </c>
+      <c r="IP5" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ5">
+        <v>1</v>
+      </c>
+      <c r="IR5" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS5">
+        <v>1</v>
+      </c>
+      <c r="IT5" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU5" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV5" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW5" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX5" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY5">
         <v>86400</v>
       </c>
-      <c r="IN5" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO5">
-        <v>1</v>
-      </c>
-      <c r="IP5" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ5">
-        <v>1</v>
-      </c>
-      <c r="IR5" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS5" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT5" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU5" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV5" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW5">
+      <c r="IZ5">
         <v>86400</v>
       </c>
-      <c r="IX5">
-        <v>86400</v>
-      </c>
-      <c r="IY5">
+      <c r="JA5">
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:259">
+    <row r="6" spans="1:261">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -4960,13 +4928,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>3125000</v>
+        <v>2896000</v>
       </c>
       <c r="O6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4981,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W6">
         <v>3</v>
@@ -4996,7 +4964,7 @@
         <v>20</v>
       </c>
       <c r="Z6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -5008,13 +4976,13 @@
         <v>20</v>
       </c>
       <c r="AD6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE6">
         <v>3</v>
       </c>
       <c r="AF6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG6">
         <v>3</v>
@@ -5029,7 +4997,7 @@
         <v>6</v>
       </c>
       <c r="AM6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN6">
         <v>1</v>
@@ -5044,10 +5012,10 @@
         <v>9</v>
       </c>
       <c r="AR6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT6">
         <v>3</v>
@@ -5059,7 +5027,7 @@
         <v>20</v>
       </c>
       <c r="AW6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX6">
         <v>3</v>
@@ -5071,13 +5039,13 @@
         <v>20</v>
       </c>
       <c r="BA6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB6">
         <v>3</v>
       </c>
       <c r="BC6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD6">
         <v>3</v>
@@ -5092,13 +5060,13 @@
         <v>5500000</v>
       </c>
       <c r="BH6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="BI6">
         <v>55</v>
       </c>
       <c r="BJ6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK6">
         <v>1</v>
@@ -5113,10 +5081,10 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ6">
         <v>3</v>
@@ -5128,7 +5096,7 @@
         <v>20</v>
       </c>
       <c r="BT6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU6">
         <v>3</v>
@@ -5140,13 +5108,13 @@
         <v>20</v>
       </c>
       <c r="BX6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY6">
         <v>3</v>
       </c>
       <c r="BZ6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA6">
         <v>0</v>
@@ -5155,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="CF6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG6">
         <v>1</v>
@@ -5170,10 +5138,10 @@
         <v>9</v>
       </c>
       <c r="CK6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM6">
         <v>3</v>
@@ -5185,7 +5153,7 @@
         <v>20</v>
       </c>
       <c r="CP6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ6">
         <v>3</v>
@@ -5197,40 +5165,25 @@
         <v>20</v>
       </c>
       <c r="CT6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU6">
         <v>3</v>
       </c>
       <c r="CV6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW6">
         <v>3</v>
       </c>
       <c r="CX6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY6">
-        <v>1</v>
-      </c>
-      <c r="CZ6">
-        <v>4900</v>
-      </c>
-      <c r="DA6" t="s">
-        <v>291</v>
-      </c>
-      <c r="DB6">
-        <v>0</v>
-      </c>
-      <c r="DC6">
-        <v>40</v>
-      </c>
-      <c r="DD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF6">
         <v>1</v>
@@ -5245,10 +5198,10 @@
         <v>9</v>
       </c>
       <c r="DJ6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL6">
         <v>3</v>
@@ -5260,7 +5213,7 @@
         <v>20</v>
       </c>
       <c r="DO6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP6">
         <v>3</v>
@@ -5272,13 +5225,13 @@
         <v>20</v>
       </c>
       <c r="DS6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT6">
         <v>3</v>
       </c>
       <c r="DU6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV6">
         <v>3</v>
@@ -5293,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED6">
         <v>1</v>
@@ -5308,10 +5261,10 @@
         <v>9</v>
       </c>
       <c r="EH6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ6">
         <v>3</v>
@@ -5323,7 +5276,7 @@
         <v>20</v>
       </c>
       <c r="EM6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN6">
         <v>3</v>
@@ -5335,13 +5288,13 @@
         <v>20</v>
       </c>
       <c r="EQ6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER6">
         <v>3</v>
       </c>
       <c r="ES6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET6">
         <v>3</v>
@@ -5356,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="FA6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB6">
         <v>1</v>
@@ -5371,10 +5324,10 @@
         <v>9</v>
       </c>
       <c r="FF6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH6">
         <v>3</v>
@@ -5386,7 +5339,7 @@
         <v>20</v>
       </c>
       <c r="FK6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL6">
         <v>3</v>
@@ -5398,19 +5351,19 @@
         <v>20</v>
       </c>
       <c r="FO6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP6">
         <v>3</v>
       </c>
       <c r="FQ6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR6">
         <v>3</v>
       </c>
       <c r="FS6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT6">
         <v>1</v>
@@ -5422,10 +5375,10 @@
         <v>2800</v>
       </c>
       <c r="FW6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="FX6" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY6">
         <v>1</v>
@@ -5440,10 +5393,10 @@
         <v>9</v>
       </c>
       <c r="GC6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE6">
         <v>3</v>
@@ -5455,7 +5408,7 @@
         <v>20</v>
       </c>
       <c r="GH6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI6">
         <v>3</v>
@@ -5467,28 +5420,28 @@
         <v>20</v>
       </c>
       <c r="GL6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM6">
         <v>3</v>
       </c>
       <c r="GN6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO6">
         <v>3</v>
       </c>
       <c r="GP6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ6">
         <v>1</v>
       </c>
       <c r="GR6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="GS6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="GT6">
         <v>100000</v>
@@ -5514,14 +5467,41 @@
       <c r="HA6" t="b">
         <v>0</v>
       </c>
+      <c r="HB6" t="s">
+        <v>299</v>
+      </c>
+      <c r="HC6">
+        <v>75000</v>
+      </c>
+      <c r="HD6">
+        <v>7200</v>
+      </c>
+      <c r="HE6">
+        <v>11000</v>
+      </c>
+      <c r="HF6">
+        <v>100000</v>
+      </c>
+      <c r="HG6">
+        <v>0.9</v>
+      </c>
+      <c r="HH6">
+        <v>0.8</v>
+      </c>
+      <c r="HI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="HJ6" t="b">
+        <v>0</v>
+      </c>
       <c r="HK6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL6">
         <v>0.05</v>
       </c>
       <c r="HM6">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN6">
         <v>0.8</v>
@@ -5530,40 +5510,22 @@
         <v>8.5</v>
       </c>
       <c r="HP6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HT6">
-        <v>1</v>
-      </c>
-      <c r="HU6">
-        <v>3100</v>
-      </c>
-      <c r="HV6">
-        <v>3100</v>
-      </c>
-      <c r="HW6">
-        <v>0.95</v>
-      </c>
-      <c r="HX6">
-        <v>0.1</v>
-      </c>
-      <c r="HY6" t="b">
-        <v>0</v>
-      </c>
-      <c r="HZ6" t="b">
         <v>0</v>
       </c>
       <c r="IA6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB6">
         <v>1</v>
@@ -5584,72 +5546,78 @@
         <v>0.5</v>
       </c>
       <c r="IH6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK6">
         <v>86400</v>
       </c>
       <c r="IL6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM6">
+        <v>43200</v>
+      </c>
+      <c r="IN6">
+        <v>1</v>
+      </c>
+      <c r="IO6">
+        <v>0</v>
+      </c>
+      <c r="IP6" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ6">
+        <v>1</v>
+      </c>
+      <c r="IR6" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS6">
+        <v>1</v>
+      </c>
+      <c r="IT6" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU6" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV6" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW6" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX6" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY6">
         <v>86400</v>
       </c>
-      <c r="IN6" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO6">
-        <v>1</v>
-      </c>
-      <c r="IP6" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ6">
-        <v>1</v>
-      </c>
-      <c r="IR6" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS6" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT6" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU6" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV6" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW6">
+      <c r="IZ6">
         <v>86400</v>
       </c>
-      <c r="IX6">
-        <v>86400</v>
-      </c>
-      <c r="IY6">
+      <c r="JA6">
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:259">
+    <row r="7" spans="1:261">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -5658,7 +5626,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -5670,13 +5638,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3648000</v>
+        <v>3863000</v>
       </c>
       <c r="O7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -5691,10 +5659,10 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W7">
         <v>3</v>
@@ -5706,7 +5674,7 @@
         <v>20</v>
       </c>
       <c r="Z7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA7">
         <v>3</v>
@@ -5718,13 +5686,13 @@
         <v>20</v>
       </c>
       <c r="AD7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE7">
         <v>3</v>
       </c>
       <c r="AF7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG7">
         <v>3</v>
@@ -5739,7 +5707,7 @@
         <v>6</v>
       </c>
       <c r="AM7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -5754,10 +5722,10 @@
         <v>9</v>
       </c>
       <c r="AR7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT7">
         <v>3</v>
@@ -5769,7 +5737,7 @@
         <v>20</v>
       </c>
       <c r="AW7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX7">
         <v>3</v>
@@ -5781,13 +5749,13 @@
         <v>20</v>
       </c>
       <c r="BA7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB7">
         <v>3</v>
       </c>
       <c r="BC7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD7">
         <v>3</v>
@@ -5799,16 +5767,16 @@
         <v>1</v>
       </c>
       <c r="BG7">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BH7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="BI7">
         <v>55</v>
       </c>
       <c r="BJ7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK7">
         <v>1</v>
@@ -5823,10 +5791,10 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ7">
         <v>3</v>
@@ -5838,7 +5806,7 @@
         <v>20</v>
       </c>
       <c r="BT7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU7">
         <v>3</v>
@@ -5850,13 +5818,13 @@
         <v>20</v>
       </c>
       <c r="BX7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY7">
         <v>3</v>
       </c>
       <c r="BZ7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA7">
         <v>0</v>
@@ -5865,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="CF7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG7">
         <v>1</v>
@@ -5880,10 +5848,10 @@
         <v>9</v>
       </c>
       <c r="CK7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM7">
         <v>3</v>
@@ -5895,7 +5863,7 @@
         <v>20</v>
       </c>
       <c r="CP7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ7">
         <v>3</v>
@@ -5907,13 +5875,13 @@
         <v>20</v>
       </c>
       <c r="CT7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU7">
         <v>3</v>
       </c>
       <c r="CV7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW7">
         <v>3</v>
@@ -5925,10 +5893,10 @@
         <v>1</v>
       </c>
       <c r="CZ7">
-        <v>4400</v>
+        <v>5800</v>
       </c>
       <c r="DA7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DB7">
         <v>0</v>
@@ -5940,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF7">
         <v>1</v>
@@ -5955,10 +5923,10 @@
         <v>9</v>
       </c>
       <c r="DJ7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL7">
         <v>3</v>
@@ -5970,7 +5938,7 @@
         <v>20</v>
       </c>
       <c r="DO7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP7">
         <v>3</v>
@@ -5982,13 +5950,13 @@
         <v>20</v>
       </c>
       <c r="DS7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT7">
         <v>3</v>
       </c>
       <c r="DU7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV7">
         <v>3</v>
@@ -6003,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED7">
         <v>1</v>
@@ -6018,10 +5986,10 @@
         <v>9</v>
       </c>
       <c r="EH7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ7">
         <v>3</v>
@@ -6033,7 +6001,7 @@
         <v>20</v>
       </c>
       <c r="EM7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN7">
         <v>3</v>
@@ -6045,13 +6013,13 @@
         <v>20</v>
       </c>
       <c r="EQ7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER7">
         <v>3</v>
       </c>
       <c r="ES7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET7">
         <v>3</v>
@@ -6066,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="FA7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB7">
         <v>1</v>
@@ -6081,10 +6049,10 @@
         <v>9</v>
       </c>
       <c r="FF7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH7">
         <v>3</v>
@@ -6096,7 +6064,7 @@
         <v>20</v>
       </c>
       <c r="FK7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL7">
         <v>3</v>
@@ -6108,19 +6076,19 @@
         <v>20</v>
       </c>
       <c r="FO7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP7">
         <v>3</v>
       </c>
       <c r="FQ7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR7">
         <v>3</v>
       </c>
       <c r="FS7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT7">
         <v>1</v>
@@ -6129,13 +6097,13 @@
         <v>1</v>
       </c>
       <c r="FV7">
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="FW7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="FX7" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY7">
         <v>1</v>
@@ -6150,10 +6118,10 @@
         <v>9</v>
       </c>
       <c r="GC7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE7">
         <v>3</v>
@@ -6165,7 +6133,7 @@
         <v>20</v>
       </c>
       <c r="GH7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI7">
         <v>3</v>
@@ -6177,34 +6145,61 @@
         <v>20</v>
       </c>
       <c r="GL7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM7">
         <v>3</v>
       </c>
       <c r="GN7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO7">
         <v>3</v>
       </c>
       <c r="GP7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GR7">
+        <v>1</v>
+      </c>
+      <c r="GS7" t="s">
+        <v>300</v>
+      </c>
+      <c r="GT7">
+        <v>50000</v>
+      </c>
+      <c r="GU7">
+        <v>7200</v>
+      </c>
+      <c r="GV7">
+        <v>7200</v>
+      </c>
+      <c r="GW7">
+        <v>50000</v>
+      </c>
+      <c r="GX7">
+        <v>0.9</v>
+      </c>
+      <c r="GY7">
+        <v>0.8</v>
+      </c>
+      <c r="GZ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="HA7" t="b">
         <v>0</v>
       </c>
       <c r="HK7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL7">
         <v>0.05</v>
       </c>
       <c r="HM7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN7">
         <v>0.8</v>
@@ -6213,13 +6208,13 @@
         <v>8.5</v>
       </c>
       <c r="HP7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS7">
         <v>1</v>
@@ -6228,10 +6223,10 @@
         <v>1</v>
       </c>
       <c r="HU7">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="HV7">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="HW7">
         <v>0.95</v>
@@ -6246,7 +6241,7 @@
         <v>0</v>
       </c>
       <c r="IA7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB7">
         <v>1</v>
@@ -6255,10 +6250,10 @@
         <v>1</v>
       </c>
       <c r="ID7">
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="IE7">
-        <v>19500</v>
+        <v>5500</v>
       </c>
       <c r="IF7">
         <v>0.95</v>
@@ -6267,72 +6262,78 @@
         <v>0.5</v>
       </c>
       <c r="IH7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK7">
         <v>86400</v>
       </c>
       <c r="IL7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM7">
+        <v>72000</v>
+      </c>
+      <c r="IN7">
+        <v>1</v>
+      </c>
+      <c r="IO7">
+        <v>0</v>
+      </c>
+      <c r="IP7" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ7">
+        <v>1</v>
+      </c>
+      <c r="IR7" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS7">
+        <v>1</v>
+      </c>
+      <c r="IT7" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU7" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV7" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW7" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX7" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY7">
         <v>86400</v>
       </c>
-      <c r="IN7" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO7">
-        <v>1</v>
-      </c>
-      <c r="IP7" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ7">
-        <v>1</v>
-      </c>
-      <c r="IR7" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS7" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT7" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU7" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV7" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW7">
+      <c r="IZ7">
         <v>86400</v>
       </c>
-      <c r="IX7">
-        <v>86400</v>
-      </c>
-      <c r="IY7">
+      <c r="JA7">
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:259">
+    <row r="8" spans="1:261">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -6341,7 +6342,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -6356,10 +6357,10 @@
         <v>3125000</v>
       </c>
       <c r="O8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -6374,10 +6375,10 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W8">
         <v>3</v>
@@ -6389,7 +6390,7 @@
         <v>20</v>
       </c>
       <c r="Z8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA8">
         <v>3</v>
@@ -6401,13 +6402,13 @@
         <v>20</v>
       </c>
       <c r="AD8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE8">
         <v>3</v>
       </c>
       <c r="AF8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG8">
         <v>3</v>
@@ -6422,7 +6423,7 @@
         <v>6</v>
       </c>
       <c r="AM8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN8">
         <v>1</v>
@@ -6437,10 +6438,10 @@
         <v>9</v>
       </c>
       <c r="AR8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT8">
         <v>3</v>
@@ -6452,7 +6453,7 @@
         <v>20</v>
       </c>
       <c r="AW8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX8">
         <v>3</v>
@@ -6464,13 +6465,13 @@
         <v>20</v>
       </c>
       <c r="BA8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB8">
         <v>3</v>
       </c>
       <c r="BC8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD8">
         <v>3</v>
@@ -6482,16 +6483,16 @@
         <v>1</v>
       </c>
       <c r="BG8">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BH8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="BI8">
         <v>55</v>
       </c>
       <c r="BJ8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK8">
         <v>1</v>
@@ -6506,10 +6507,10 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ8">
         <v>3</v>
@@ -6521,7 +6522,7 @@
         <v>20</v>
       </c>
       <c r="BT8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU8">
         <v>3</v>
@@ -6533,13 +6534,13 @@
         <v>20</v>
       </c>
       <c r="BX8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY8">
         <v>3</v>
       </c>
       <c r="BZ8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA8">
         <v>0</v>
@@ -6548,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="CF8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG8">
         <v>1</v>
@@ -6563,10 +6564,10 @@
         <v>9</v>
       </c>
       <c r="CK8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM8">
         <v>3</v>
@@ -6578,7 +6579,7 @@
         <v>20</v>
       </c>
       <c r="CP8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ8">
         <v>3</v>
@@ -6590,40 +6591,25 @@
         <v>20</v>
       </c>
       <c r="CT8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU8">
         <v>3</v>
       </c>
       <c r="CV8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW8">
         <v>3</v>
       </c>
       <c r="CX8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY8">
-        <v>1</v>
-      </c>
-      <c r="CZ8">
-        <v>5300</v>
-      </c>
-      <c r="DA8" t="s">
-        <v>291</v>
-      </c>
-      <c r="DB8">
-        <v>-20</v>
-      </c>
-      <c r="DC8">
-        <v>50</v>
-      </c>
-      <c r="DD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF8">
         <v>1</v>
@@ -6638,10 +6624,10 @@
         <v>9</v>
       </c>
       <c r="DJ8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL8">
         <v>3</v>
@@ -6653,7 +6639,7 @@
         <v>20</v>
       </c>
       <c r="DO8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP8">
         <v>3</v>
@@ -6665,13 +6651,13 @@
         <v>20</v>
       </c>
       <c r="DS8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT8">
         <v>3</v>
       </c>
       <c r="DU8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV8">
         <v>3</v>
@@ -6686,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED8">
         <v>1</v>
@@ -6701,10 +6687,10 @@
         <v>9</v>
       </c>
       <c r="EH8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ8">
         <v>3</v>
@@ -6716,7 +6702,7 @@
         <v>20</v>
       </c>
       <c r="EM8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN8">
         <v>3</v>
@@ -6728,13 +6714,13 @@
         <v>20</v>
       </c>
       <c r="EQ8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER8">
         <v>3</v>
       </c>
       <c r="ES8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET8">
         <v>3</v>
@@ -6749,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="FA8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB8">
         <v>1</v>
@@ -6764,10 +6750,10 @@
         <v>9</v>
       </c>
       <c r="FF8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH8">
         <v>3</v>
@@ -6779,7 +6765,7 @@
         <v>20</v>
       </c>
       <c r="FK8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL8">
         <v>3</v>
@@ -6791,19 +6777,19 @@
         <v>20</v>
       </c>
       <c r="FO8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP8">
         <v>3</v>
       </c>
       <c r="FQ8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR8">
         <v>3</v>
       </c>
       <c r="FS8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT8">
         <v>1</v>
@@ -6812,13 +6798,13 @@
         <v>1</v>
       </c>
       <c r="FV8">
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="FW8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="FX8" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY8">
         <v>1</v>
@@ -6833,10 +6819,10 @@
         <v>9</v>
       </c>
       <c r="GC8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE8">
         <v>3</v>
@@ -6848,7 +6834,7 @@
         <v>20</v>
       </c>
       <c r="GH8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI8">
         <v>3</v>
@@ -6860,19 +6846,19 @@
         <v>20</v>
       </c>
       <c r="GL8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM8">
         <v>3</v>
       </c>
       <c r="GN8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO8">
         <v>3</v>
       </c>
       <c r="GP8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ8">
         <v>1</v>
@@ -6884,16 +6870,16 @@
         <v>301</v>
       </c>
       <c r="GT8">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="GU8">
         <v>7200</v>
       </c>
       <c r="GV8">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GW8">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="GX8">
         <v>0.9</v>
@@ -6908,13 +6894,13 @@
         <v>0</v>
       </c>
       <c r="HK8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL8">
         <v>0.05</v>
       </c>
       <c r="HM8">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN8">
         <v>0.8</v>
@@ -6923,40 +6909,22 @@
         <v>8.5</v>
       </c>
       <c r="HP8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HT8">
-        <v>1</v>
-      </c>
-      <c r="HU8">
-        <v>3100</v>
-      </c>
-      <c r="HV8">
-        <v>3100</v>
-      </c>
-      <c r="HW8">
-        <v>0.95</v>
-      </c>
-      <c r="HX8">
-        <v>0.1</v>
-      </c>
-      <c r="HY8" t="b">
-        <v>0</v>
-      </c>
-      <c r="HZ8" t="b">
         <v>0</v>
       </c>
       <c r="IA8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB8">
         <v>1</v>
@@ -6965,10 +6933,10 @@
         <v>1</v>
       </c>
       <c r="ID8">
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="IE8">
-        <v>19500</v>
+        <v>5500</v>
       </c>
       <c r="IF8">
         <v>0.95</v>
@@ -6977,72 +6945,78 @@
         <v>0.5</v>
       </c>
       <c r="IH8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK8">
         <v>86400</v>
       </c>
       <c r="IL8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM8">
         <v>86400</v>
       </c>
-      <c r="IN8" t="s">
-        <v>289</v>
+      <c r="IN8">
+        <v>1</v>
       </c>
       <c r="IO8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IP8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="IQ8">
         <v>1</v>
       </c>
       <c r="IR8" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS8" t="s">
-        <v>289</v>
+        <v>290</v>
+      </c>
+      <c r="IS8">
+        <v>1</v>
       </c>
       <c r="IT8" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="IU8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="IV8" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW8">
+        <v>290</v>
+      </c>
+      <c r="IW8" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX8" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY8">
         <v>86400</v>
       </c>
-      <c r="IX8">
+      <c r="IZ8">
         <v>86400</v>
       </c>
-      <c r="IY8">
+      <c r="JA8">
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:259">
+    <row r="9" spans="1:261">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -7051,7 +7025,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7066,10 +7040,10 @@
         <v>5527000</v>
       </c>
       <c r="O9" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="P9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -7084,10 +7058,10 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W9">
         <v>3</v>
@@ -7099,7 +7073,7 @@
         <v>20</v>
       </c>
       <c r="Z9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA9">
         <v>3</v>
@@ -7111,13 +7085,13 @@
         <v>20</v>
       </c>
       <c r="AD9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE9">
         <v>3</v>
       </c>
       <c r="AF9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG9">
         <v>3</v>
@@ -7132,7 +7106,7 @@
         <v>6</v>
       </c>
       <c r="AM9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN9">
         <v>1</v>
@@ -7147,10 +7121,10 @@
         <v>9</v>
       </c>
       <c r="AR9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT9">
         <v>3</v>
@@ -7162,7 +7136,7 @@
         <v>20</v>
       </c>
       <c r="AW9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX9">
         <v>3</v>
@@ -7174,13 +7148,13 @@
         <v>20</v>
       </c>
       <c r="BA9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB9">
         <v>3</v>
       </c>
       <c r="BC9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD9">
         <v>3</v>
@@ -7192,16 +7166,16 @@
         <v>1</v>
       </c>
       <c r="BG9">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BH9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="BI9">
         <v>55</v>
       </c>
       <c r="BJ9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK9">
         <v>1</v>
@@ -7216,10 +7190,10 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ9">
         <v>3</v>
@@ -7231,7 +7205,7 @@
         <v>20</v>
       </c>
       <c r="BT9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU9">
         <v>3</v>
@@ -7243,13 +7217,13 @@
         <v>20</v>
       </c>
       <c r="BX9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY9">
         <v>3</v>
       </c>
       <c r="BZ9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA9">
         <v>0</v>
@@ -7258,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="CF9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG9">
         <v>1</v>
@@ -7273,10 +7247,10 @@
         <v>9</v>
       </c>
       <c r="CK9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM9">
         <v>3</v>
@@ -7288,7 +7262,7 @@
         <v>20</v>
       </c>
       <c r="CP9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ9">
         <v>3</v>
@@ -7300,13 +7274,13 @@
         <v>20</v>
       </c>
       <c r="CT9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU9">
         <v>3</v>
       </c>
       <c r="CV9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW9">
         <v>3</v>
@@ -7318,22 +7292,22 @@
         <v>1</v>
       </c>
       <c r="CZ9">
-        <v>8700</v>
+        <v>9800</v>
       </c>
       <c r="DA9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DB9">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="DC9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DD9" t="b">
         <v>1</v>
       </c>
       <c r="DE9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF9">
         <v>1</v>
@@ -7348,10 +7322,10 @@
         <v>9</v>
       </c>
       <c r="DJ9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL9">
         <v>3</v>
@@ -7363,7 +7337,7 @@
         <v>20</v>
       </c>
       <c r="DO9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP9">
         <v>3</v>
@@ -7375,13 +7349,13 @@
         <v>20</v>
       </c>
       <c r="DS9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT9">
         <v>3</v>
       </c>
       <c r="DU9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV9">
         <v>3</v>
@@ -7396,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED9">
         <v>1</v>
@@ -7411,10 +7385,10 @@
         <v>9</v>
       </c>
       <c r="EH9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ9">
         <v>3</v>
@@ -7426,7 +7400,7 @@
         <v>20</v>
       </c>
       <c r="EM9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN9">
         <v>3</v>
@@ -7438,13 +7412,13 @@
         <v>20</v>
       </c>
       <c r="EQ9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER9">
         <v>3</v>
       </c>
       <c r="ES9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET9">
         <v>3</v>
@@ -7459,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="FA9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB9">
         <v>1</v>
@@ -7474,10 +7448,10 @@
         <v>9</v>
       </c>
       <c r="FF9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH9">
         <v>3</v>
@@ -7489,7 +7463,7 @@
         <v>20</v>
       </c>
       <c r="FK9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL9">
         <v>3</v>
@@ -7501,19 +7475,19 @@
         <v>20</v>
       </c>
       <c r="FO9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP9">
         <v>3</v>
       </c>
       <c r="FQ9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR9">
         <v>3</v>
       </c>
       <c r="FS9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT9">
         <v>1</v>
@@ -7522,13 +7496,13 @@
         <v>1</v>
       </c>
       <c r="FV9">
-        <v>2800</v>
+        <v>9800</v>
       </c>
       <c r="FW9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="FX9" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY9">
         <v>1</v>
@@ -7543,10 +7517,10 @@
         <v>9</v>
       </c>
       <c r="GC9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE9">
         <v>3</v>
@@ -7558,7 +7532,7 @@
         <v>20</v>
       </c>
       <c r="GH9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI9">
         <v>3</v>
@@ -7570,19 +7544,19 @@
         <v>20</v>
       </c>
       <c r="GL9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM9">
         <v>3</v>
       </c>
       <c r="GN9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO9">
         <v>3</v>
       </c>
       <c r="GP9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ9">
         <v>0</v>
@@ -7591,13 +7565,13 @@
         <v>0</v>
       </c>
       <c r="HK9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL9">
         <v>0.05</v>
       </c>
       <c r="HM9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN9">
         <v>0.8</v>
@@ -7606,13 +7580,13 @@
         <v>8.5</v>
       </c>
       <c r="HP9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS9">
         <v>1</v>
@@ -7639,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="IA9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB9">
         <v>1</v>
@@ -7648,10 +7622,10 @@
         <v>1</v>
       </c>
       <c r="ID9">
-        <v>2800</v>
+        <v>9800</v>
       </c>
       <c r="IE9">
-        <v>5500</v>
+        <v>19500</v>
       </c>
       <c r="IF9">
         <v>0.95</v>
@@ -7660,66 +7634,72 @@
         <v>0.5</v>
       </c>
       <c r="IH9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK9">
         <v>86400</v>
       </c>
       <c r="IL9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM9">
+        <v>43200</v>
+      </c>
+      <c r="IN9">
+        <v>1</v>
+      </c>
+      <c r="IO9">
+        <v>0</v>
+      </c>
+      <c r="IP9" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ9">
+        <v>1</v>
+      </c>
+      <c r="IR9" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS9">
+        <v>1</v>
+      </c>
+      <c r="IT9" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU9" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV9" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW9" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX9" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY9">
         <v>86400</v>
       </c>
-      <c r="IN9" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO9">
-        <v>1</v>
-      </c>
-      <c r="IP9" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ9">
-        <v>1</v>
-      </c>
-      <c r="IR9" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS9" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT9" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU9" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV9" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW9">
+      <c r="IZ9">
         <v>86400</v>
       </c>
-      <c r="IX9">
-        <v>86400</v>
-      </c>
-      <c r="IY9">
+      <c r="JA9">
         <v>3600</v>
       </c>
     </row>
-    <row r="10" spans="1:259">
+    <row r="10" spans="1:261">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -7746,13 +7726,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>4402000</v>
+        <v>4536000</v>
       </c>
       <c r="O10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="P10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -7767,10 +7747,10 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W10">
         <v>3</v>
@@ -7782,7 +7762,7 @@
         <v>20</v>
       </c>
       <c r="Z10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA10">
         <v>3</v>
@@ -7794,13 +7774,13 @@
         <v>20</v>
       </c>
       <c r="AD10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE10">
         <v>3</v>
       </c>
       <c r="AF10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG10">
         <v>3</v>
@@ -7815,7 +7795,7 @@
         <v>6</v>
       </c>
       <c r="AM10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN10">
         <v>1</v>
@@ -7830,10 +7810,10 @@
         <v>9</v>
       </c>
       <c r="AR10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT10">
         <v>3</v>
@@ -7845,7 +7825,7 @@
         <v>20</v>
       </c>
       <c r="AW10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX10">
         <v>3</v>
@@ -7857,13 +7837,13 @@
         <v>20</v>
       </c>
       <c r="BA10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB10">
         <v>3</v>
       </c>
       <c r="BC10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD10">
         <v>3</v>
@@ -7878,13 +7858,13 @@
         <v>5500000</v>
       </c>
       <c r="BH10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="BI10">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BJ10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK10">
         <v>1</v>
@@ -7899,10 +7879,10 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ10">
         <v>3</v>
@@ -7914,7 +7894,7 @@
         <v>20</v>
       </c>
       <c r="BT10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU10">
         <v>3</v>
@@ -7926,13 +7906,13 @@
         <v>20</v>
       </c>
       <c r="BX10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY10">
         <v>3</v>
       </c>
       <c r="BZ10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA10">
         <v>0</v>
@@ -7941,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="CF10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG10">
         <v>1</v>
@@ -7956,10 +7936,10 @@
         <v>9</v>
       </c>
       <c r="CK10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM10">
         <v>3</v>
@@ -7971,7 +7951,7 @@
         <v>20</v>
       </c>
       <c r="CP10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ10">
         <v>3</v>
@@ -7983,13 +7963,13 @@
         <v>20</v>
       </c>
       <c r="CT10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU10">
         <v>3</v>
       </c>
       <c r="CV10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW10">
         <v>3</v>
@@ -8001,7 +7981,7 @@
         <v>0</v>
       </c>
       <c r="DE10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF10">
         <v>1</v>
@@ -8016,10 +7996,10 @@
         <v>9</v>
       </c>
       <c r="DJ10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL10">
         <v>3</v>
@@ -8031,7 +8011,7 @@
         <v>20</v>
       </c>
       <c r="DO10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP10">
         <v>3</v>
@@ -8043,13 +8023,13 @@
         <v>20</v>
       </c>
       <c r="DS10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT10">
         <v>3</v>
       </c>
       <c r="DU10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV10">
         <v>3</v>
@@ -8064,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED10">
         <v>1</v>
@@ -8079,10 +8059,10 @@
         <v>9</v>
       </c>
       <c r="EH10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ10">
         <v>3</v>
@@ -8094,7 +8074,7 @@
         <v>20</v>
       </c>
       <c r="EM10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN10">
         <v>3</v>
@@ -8106,13 +8086,13 @@
         <v>20</v>
       </c>
       <c r="EQ10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER10">
         <v>3</v>
       </c>
       <c r="ES10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET10">
         <v>3</v>
@@ -8127,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="FA10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB10">
         <v>1</v>
@@ -8142,10 +8122,10 @@
         <v>9</v>
       </c>
       <c r="FF10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH10">
         <v>3</v>
@@ -8157,7 +8137,7 @@
         <v>20</v>
       </c>
       <c r="FK10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL10">
         <v>3</v>
@@ -8169,19 +8149,19 @@
         <v>20</v>
       </c>
       <c r="FO10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP10">
         <v>3</v>
       </c>
       <c r="FQ10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR10">
         <v>3</v>
       </c>
       <c r="FS10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT10">
         <v>1</v>
@@ -8193,10 +8173,10 @@
         <v>2800</v>
       </c>
       <c r="FW10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="FX10" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY10">
         <v>1</v>
@@ -8211,10 +8191,10 @@
         <v>9</v>
       </c>
       <c r="GC10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE10">
         <v>3</v>
@@ -8226,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="GH10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI10">
         <v>3</v>
@@ -8238,34 +8218,61 @@
         <v>20</v>
       </c>
       <c r="GL10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM10">
         <v>3</v>
       </c>
       <c r="GN10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO10">
         <v>3</v>
       </c>
       <c r="GP10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GR10">
+        <v>1</v>
+      </c>
+      <c r="GS10" t="s">
+        <v>302</v>
+      </c>
+      <c r="GT10">
+        <v>50000</v>
+      </c>
+      <c r="GU10">
+        <v>7200</v>
+      </c>
+      <c r="GV10">
+        <v>7200</v>
+      </c>
+      <c r="GW10">
+        <v>50000</v>
+      </c>
+      <c r="GX10">
+        <v>0.9</v>
+      </c>
+      <c r="GY10">
+        <v>0.8</v>
+      </c>
+      <c r="GZ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="HA10" t="b">
         <v>0</v>
       </c>
       <c r="HK10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL10">
         <v>0.05</v>
       </c>
       <c r="HM10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN10">
         <v>0.8</v>
@@ -8274,13 +8281,13 @@
         <v>8.5</v>
       </c>
       <c r="HP10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS10">
         <v>0</v>
@@ -8289,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="IA10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB10">
         <v>1</v>
@@ -8310,72 +8317,78 @@
         <v>0.5</v>
       </c>
       <c r="IH10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK10">
         <v>86400</v>
       </c>
       <c r="IL10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM10">
+        <v>57600</v>
+      </c>
+      <c r="IN10">
+        <v>1</v>
+      </c>
+      <c r="IO10">
+        <v>0</v>
+      </c>
+      <c r="IP10" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ10">
+        <v>1</v>
+      </c>
+      <c r="IR10" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS10">
+        <v>1</v>
+      </c>
+      <c r="IT10" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU10" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV10" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW10" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX10" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY10">
         <v>86400</v>
       </c>
-      <c r="IN10" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO10">
-        <v>1</v>
-      </c>
-      <c r="IP10" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ10">
-        <v>1</v>
-      </c>
-      <c r="IR10" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS10" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT10" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU10" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV10" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW10">
+      <c r="IZ10">
         <v>86400</v>
       </c>
-      <c r="IX10">
-        <v>86400</v>
-      </c>
-      <c r="IY10">
+      <c r="JA10">
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:259">
+    <row r="11" spans="1:261">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -8384,7 +8397,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -8396,13 +8409,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>2532000</v>
+        <v>5527000</v>
       </c>
       <c r="O11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -8417,10 +8430,10 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="V11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="W11">
         <v>3</v>
@@ -8432,7 +8445,7 @@
         <v>20</v>
       </c>
       <c r="Z11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA11">
         <v>3</v>
@@ -8444,13 +8457,13 @@
         <v>20</v>
       </c>
       <c r="AD11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AE11">
         <v>3</v>
       </c>
       <c r="AF11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG11">
         <v>3</v>
@@ -8465,7 +8478,7 @@
         <v>6</v>
       </c>
       <c r="AM11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -8480,10 +8493,10 @@
         <v>9</v>
       </c>
       <c r="AR11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AS11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AT11">
         <v>3</v>
@@ -8495,7 +8508,7 @@
         <v>20</v>
       </c>
       <c r="AW11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AX11">
         <v>3</v>
@@ -8507,13 +8520,13 @@
         <v>20</v>
       </c>
       <c r="BA11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB11">
         <v>3</v>
       </c>
       <c r="BC11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BD11">
         <v>3</v>
@@ -8525,16 +8538,16 @@
         <v>1</v>
       </c>
       <c r="BG11">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BH11" t="s">
         <v>288</v>
       </c>
       <c r="BI11">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BJ11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="BK11">
         <v>1</v>
@@ -8549,10 +8562,10 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BP11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BQ11">
         <v>3</v>
@@ -8564,7 +8577,7 @@
         <v>20</v>
       </c>
       <c r="BT11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BU11">
         <v>3</v>
@@ -8576,13 +8589,13 @@
         <v>20</v>
       </c>
       <c r="BX11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY11">
         <v>3</v>
       </c>
       <c r="BZ11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CA11">
         <v>0</v>
@@ -8591,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="CF11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="CG11">
         <v>1</v>
@@ -8606,10 +8619,10 @@
         <v>9</v>
       </c>
       <c r="CK11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="CL11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CM11">
         <v>3</v>
@@ -8621,7 +8634,7 @@
         <v>20</v>
       </c>
       <c r="CP11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CQ11">
         <v>3</v>
@@ -8633,13 +8646,13 @@
         <v>20</v>
       </c>
       <c r="CT11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="CU11">
         <v>3</v>
       </c>
       <c r="CV11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="CW11">
         <v>3</v>
@@ -8651,10 +8664,10 @@
         <v>1</v>
       </c>
       <c r="CZ11">
-        <v>3200</v>
+        <v>7900</v>
       </c>
       <c r="DA11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="DB11">
         <v>0</v>
@@ -8666,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="DE11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="DF11">
         <v>1</v>
@@ -8681,10 +8694,10 @@
         <v>9</v>
       </c>
       <c r="DJ11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DK11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DL11">
         <v>3</v>
@@ -8696,7 +8709,7 @@
         <v>20</v>
       </c>
       <c r="DO11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DP11">
         <v>3</v>
@@ -8708,13 +8721,13 @@
         <v>20</v>
       </c>
       <c r="DS11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DT11">
         <v>3</v>
       </c>
       <c r="DU11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="DV11">
         <v>3</v>
@@ -8729,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="ED11">
         <v>1</v>
@@ -8744,10 +8757,10 @@
         <v>9</v>
       </c>
       <c r="EH11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EI11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EJ11">
         <v>3</v>
@@ -8759,7 +8772,7 @@
         <v>20</v>
       </c>
       <c r="EM11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EN11">
         <v>3</v>
@@ -8771,13 +8784,13 @@
         <v>20</v>
       </c>
       <c r="EQ11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="ER11">
         <v>3</v>
       </c>
       <c r="ES11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="ET11">
         <v>3</v>
@@ -8792,7 +8805,7 @@
         <v>0</v>
       </c>
       <c r="FA11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="FB11">
         <v>1</v>
@@ -8807,10 +8820,10 @@
         <v>9</v>
       </c>
       <c r="FF11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="FG11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FH11">
         <v>3</v>
@@ -8822,7 +8835,7 @@
         <v>20</v>
       </c>
       <c r="FK11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FL11">
         <v>3</v>
@@ -8834,19 +8847,19 @@
         <v>20</v>
       </c>
       <c r="FO11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="FP11">
         <v>3</v>
       </c>
       <c r="FQ11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="FR11">
         <v>3</v>
       </c>
       <c r="FS11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="FT11">
         <v>1</v>
@@ -8855,13 +8868,13 @@
         <v>1</v>
       </c>
       <c r="FV11">
-        <v>2800</v>
+        <v>9800</v>
       </c>
       <c r="FW11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="FX11" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="FY11">
         <v>1</v>
@@ -8876,10 +8889,10 @@
         <v>9</v>
       </c>
       <c r="GC11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="GD11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GE11">
         <v>3</v>
@@ -8891,7 +8904,7 @@
         <v>20</v>
       </c>
       <c r="GH11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GI11">
         <v>3</v>
@@ -8903,19 +8916,19 @@
         <v>20</v>
       </c>
       <c r="GL11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="GM11">
         <v>3</v>
       </c>
       <c r="GN11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="GO11">
         <v>3</v>
       </c>
       <c r="GP11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GQ11">
         <v>0</v>
@@ -8924,13 +8937,13 @@
         <v>0</v>
       </c>
       <c r="HK11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="HL11">
         <v>0.05</v>
       </c>
       <c r="HM11">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="HN11">
         <v>0.8</v>
@@ -8939,40 +8952,22 @@
         <v>8.5</v>
       </c>
       <c r="HP11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="HQ11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="HR11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="HS11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HT11">
-        <v>1</v>
-      </c>
-      <c r="HU11">
-        <v>2500</v>
-      </c>
-      <c r="HV11">
-        <v>2500</v>
-      </c>
-      <c r="HW11">
-        <v>0.95</v>
-      </c>
-      <c r="HX11">
-        <v>0.1</v>
-      </c>
-      <c r="HY11" t="b">
-        <v>0</v>
-      </c>
-      <c r="HZ11" t="b">
         <v>0</v>
       </c>
       <c r="IA11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="IB11">
         <v>1</v>
@@ -8981,10 +8976,10 @@
         <v>1</v>
       </c>
       <c r="ID11">
-        <v>2800</v>
+        <v>9800</v>
       </c>
       <c r="IE11">
-        <v>5500</v>
+        <v>19500</v>
       </c>
       <c r="IF11">
         <v>0.95</v>
@@ -8993,2335 +8988,64 @@
         <v>0.5</v>
       </c>
       <c r="IH11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="II11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IJ11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="IK11">
         <v>86400</v>
       </c>
       <c r="IL11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="IM11">
+        <v>72000</v>
+      </c>
+      <c r="IN11">
+        <v>1</v>
+      </c>
+      <c r="IO11">
+        <v>0</v>
+      </c>
+      <c r="IP11" t="s">
+        <v>290</v>
+      </c>
+      <c r="IQ11">
+        <v>1</v>
+      </c>
+      <c r="IR11" t="s">
+        <v>290</v>
+      </c>
+      <c r="IS11">
+        <v>1</v>
+      </c>
+      <c r="IT11" t="s">
+        <v>309</v>
+      </c>
+      <c r="IU11" t="s">
+        <v>290</v>
+      </c>
+      <c r="IV11" t="s">
+        <v>290</v>
+      </c>
+      <c r="IW11" t="s">
+        <v>290</v>
+      </c>
+      <c r="IX11" t="s">
+        <v>309</v>
+      </c>
+      <c r="IY11">
         <v>86400</v>
       </c>
-      <c r="IN11" t="s">
-        <v>289</v>
-      </c>
-      <c r="IO11">
-        <v>1</v>
-      </c>
-      <c r="IP11" t="s">
-        <v>289</v>
-      </c>
-      <c r="IQ11">
-        <v>1</v>
-      </c>
-      <c r="IR11" t="s">
-        <v>308</v>
-      </c>
-      <c r="IS11" t="s">
-        <v>289</v>
-      </c>
-      <c r="IT11" t="s">
-        <v>289</v>
-      </c>
-      <c r="IU11" t="s">
-        <v>289</v>
-      </c>
-      <c r="IV11" t="s">
-        <v>308</v>
-      </c>
-      <c r="IW11">
+      <c r="IZ11">
         <v>86400</v>
       </c>
-      <c r="IX11">
-        <v>86400</v>
-      </c>
-      <c r="IY11">
+      <c r="JA11">
         <v>3600</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:II1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="2:243">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="DA1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="DB1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="DC1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="DD1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="DE1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="DF1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="DG1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="DH1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="DJ1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="DK1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="DL1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="DM1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="DN1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="DO1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="DP1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="DQ1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="DR1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="DS1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DT1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="DU1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="DV1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="DW1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="DX1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="DY1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="DZ1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="EA1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="EB1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="EC1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="ED1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="EE1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="EF1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="EG1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="EH1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="EI1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="EJ1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="EK1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="EL1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="EM1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="EN1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="EO1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="EP1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="EQ1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="ER1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="ES1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="ET1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="EU1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="EV1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="EW1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="EX1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="EY1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="EZ1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="FA1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="FB1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="FC1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="FD1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="FE1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="FF1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="FG1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="FH1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="FI1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="FJ1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="FK1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="FL1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="FM1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="FN1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="FO1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="FP1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="FQ1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="FR1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="FS1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="FT1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="FU1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="FV1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="FW1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="FX1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="FY1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="FZ1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="GA1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="GB1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="GC1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="GD1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="GE1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="GF1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="GG1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="GH1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="GI1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="GJ1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="GK1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="GL1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="GM1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="GN1" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="GO1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="GP1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="GQ1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="GR1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="GS1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="GT1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="GU1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="GV1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="GW1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="GX1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="GY1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="GZ1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="HA1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="HB1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="HC1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="HD1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="HE1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="HF1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="HG1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="HH1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="HI1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="HJ1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="HK1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="HL1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="HM1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="HN1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="HO1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="HP1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="HQ1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="HR1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="HS1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="HT1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="HU1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="HV1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="HW1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="HX1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="HY1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="HZ1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="IA1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="IB1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="IC1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="ID1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="IE1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="IF1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="IG1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="IH1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="II1" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:FN1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="2:170">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="DA1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="DB1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="DC1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="DD1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="DE1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="DF1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="DG1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="DH1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="DJ1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="DK1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="DL1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="DM1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="DN1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="DO1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="DP1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="DQ1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="DR1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="DS1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="DT1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="DU1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="DV1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="DW1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="DX1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="DY1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="DZ1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="EA1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="EB1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="EC1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="ED1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="EE1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="EF1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="EG1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="EH1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="EI1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="EJ1" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="EK1" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="EL1" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="EM1" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="EN1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="EO1" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="EP1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="EQ1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="ER1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="ES1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="ET1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="EU1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="EV1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="EW1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="EX1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="EY1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="EZ1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="FA1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="FB1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="FC1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="FD1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="FE1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="FF1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="FG1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="FH1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="FI1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="FJ1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="FK1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="FL1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="FM1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="FN1" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:FW1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="2:179">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="DA1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="DB1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="DC1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="DD1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="DE1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="DF1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="DG1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="DH1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="DJ1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="DK1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="DL1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="DM1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="DN1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="DO1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="DP1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="DQ1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="DR1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="DS1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="DT1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="DU1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="DV1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="DW1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="DX1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="DY1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="DZ1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="EA1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="EB1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="EC1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="ED1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="EE1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="EF1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="EG1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="EH1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="EI1" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="EJ1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="EK1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="EL1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="EM1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="EN1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="EO1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="EP1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="EQ1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="ER1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="ES1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="ET1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="EU1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="EV1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="EW1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="EX1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="EY1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="EZ1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="FA1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="FB1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="FC1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="FD1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="FE1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="FF1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="FG1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="FH1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="FI1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="FJ1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="FK1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="FL1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="FM1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="FN1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="FO1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="FP1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="FQ1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="FR1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="FS1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="FT1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="FU1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="FV1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="FW1" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:CZ1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="2:104">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:AV1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="2:48">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/02_config/example_single_market/agents.xlsx
+++ b/02_config/example_single_market/agents.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\Documents\Python Scripts\HAMLET\02_config\example_single_market\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46780918-6FD3-432D-A5B0-9AA117D6CA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38590" yWindow="1280" windowWidth="28740" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sfh" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -949,8 +955,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1013,13 +1019,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1057,7 +1071,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1091,6 +1105,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1125,9 +1140,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1300,11 +1316,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:JA11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:261">
+    <row r="1" spans="1:261" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2086,7 +2102,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:261">
+    <row r="2" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2385,7 +2401,7 @@
         <v>50</v>
       </c>
       <c r="DD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="s">
         <v>290</v>
@@ -2775,7 +2791,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:261">
+    <row r="3" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3074,7 +3090,7 @@
         <v>40</v>
       </c>
       <c r="DD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="s">
         <v>290</v>
@@ -3464,7 +3480,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:261">
+    <row r="4" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3763,7 +3779,7 @@
         <v>40</v>
       </c>
       <c r="DD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="s">
         <v>290</v>
@@ -4153,7 +4169,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:261">
+    <row r="5" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4452,7 +4468,7 @@
         <v>40</v>
       </c>
       <c r="DD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="s">
         <v>290</v>
@@ -4896,7 +4912,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:261">
+    <row r="6" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -5606,7 +5622,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:261">
+    <row r="7" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -5905,7 +5921,7 @@
         <v>40</v>
       </c>
       <c r="DD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="s">
         <v>290</v>
@@ -6322,7 +6338,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:261">
+    <row r="8" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -7005,7 +7021,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:261">
+    <row r="9" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -7304,7 +7320,7 @@
         <v>50</v>
       </c>
       <c r="DD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="s">
         <v>290</v>
@@ -7694,7 +7710,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="10" spans="1:261">
+    <row r="10" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -8377,7 +8393,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:261">
+    <row r="11" spans="1:261" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -8676,7 +8692,7 @@
         <v>40</v>
       </c>
       <c r="DD11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="s">
         <v>290</v>
